--- a/AAII_Financials/Quarterly/RGP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RGP_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
   <si>
     <t>RGP</t>
   </si>
@@ -656,327 +656,339 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45255</v>
+      </c>
+      <c r="E7" s="2">
         <v>45164</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45073</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44982</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44891</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44800</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44709</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44618</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44528</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44436</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44345</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44254</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44163</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44072</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43981</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43883</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43792</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43701</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43610</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43519</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43428</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43337</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43246</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>163100</v>
+      </c>
+      <c r="E8" s="3">
         <v>170200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>184400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>186800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>200400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>204100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>217000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>204600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>200200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>183100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>172300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>156600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>153200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>147300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>178600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>168100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>184500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>172200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>182100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>179500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>188800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>178600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>183800</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>99700</v>
+      </c>
+      <c r="E9" s="3">
         <v>103200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>108700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>115200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>118000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>120600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>127400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>127800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>121500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>111700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>104000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>99600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>95000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>89400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>106400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>106600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>110100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>104700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>109200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>111600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>115400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>110400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>113400</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>63400</v>
+      </c>
+      <c r="E10" s="3">
         <v>67000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>75700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>71600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>82400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>83500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>89600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>76800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>78700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>71400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>68300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>57000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>58200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>57900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>72200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>61500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>74400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>67500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>72900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>67900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>73400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>68200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>70400</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1002,8 +1014,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1073,8 +1086,11 @@
       <c r="Y12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,64 +1160,67 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2900</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>-400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>6600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-900</v>
-      </c>
-      <c r="S14" s="3">
-        <v>-100</v>
       </c>
       <c r="T14" s="3">
         <v>-100</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
+      <c r="U14" s="3">
+        <v>-100</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
@@ -1212,16 +1231,19 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="E15" s="3">
         <v>2200</v>
@@ -1230,64 +1252,67 @@
         <v>2200</v>
       </c>
       <c r="G15" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="H15" s="3">
         <v>2100</v>
       </c>
       <c r="I15" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="J15" s="3">
         <v>2200</v>
       </c>
       <c r="K15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L15" s="3">
         <v>2100</v>
-      </c>
-      <c r="L15" s="3">
-        <v>2000</v>
       </c>
       <c r="M15" s="3">
         <v>2000</v>
       </c>
       <c r="N15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="O15" s="3">
         <v>2200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2500</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>2700</v>
       </c>
       <c r="R15" s="3">
         <v>2700</v>
       </c>
       <c r="S15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="T15" s="3">
         <v>2900</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2200</v>
-      </c>
-      <c r="V15" s="3">
-        <v>2100</v>
       </c>
       <c r="W15" s="3">
         <v>2100</v>
       </c>
       <c r="X15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="Y15" s="3">
         <v>2000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1335,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>154800</v>
+      </c>
+      <c r="E17" s="3">
         <v>165300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>167400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>179700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>176900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>178900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>188900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>187100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>180500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>165100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>156900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>154600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>152000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>143100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>171100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>164600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>166800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>164200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>168300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>169300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>172500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>168800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>174300</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E18" s="3">
         <v>4900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>17000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>23500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>25200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>28100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>17500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>19700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>18000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>15400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>7500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>17700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>8000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>13800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>10200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>16300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>9800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,8 +1511,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1488,141 +1521,147 @@
         <v>300</v>
       </c>
       <c r="E20" s="3">
+        <v>300</v>
+      </c>
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
         <v>-300</v>
       </c>
       <c r="K20" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="L20" s="3">
         <v>100</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>100</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-500</v>
       </c>
       <c r="R20" s="3">
         <v>-500</v>
       </c>
       <c r="S20" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>10800</v>
+      </c>
+      <c r="E21" s="3">
         <v>7400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>19300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>9200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>25400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>27300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>29900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>19400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>21900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>20100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>17500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>3900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>9700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>5600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>20600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>10000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>16200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>12400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>18500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>11900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1659,8 +1698,8 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>8</v>
+      <c r="O22" s="3">
+        <v>0</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>8</v>
@@ -1677,14 +1716,14 @@
       <c r="T22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V22" s="3">
         <v>600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>700</v>
-      </c>
-      <c r="W22" s="3">
-        <v>600</v>
       </c>
       <c r="X22" s="3">
         <v>600</v>
@@ -1692,150 +1731,159 @@
       <c r="Y22" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E23" s="3">
         <v>5200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>17200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>23300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>25100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>27800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>17200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>19900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>18100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>15400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>7000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>17700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>7600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>13400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>9600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>15700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>9200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E24" s="3">
         <v>2100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5400</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>5900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-2200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-7800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-4000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>4000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1953,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E26" s="3">
         <v>3100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>11800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>7000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>17400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>18100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>20500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>19400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>14300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>12900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>23200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-1000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>6900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>12300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>9400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>5800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>10600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E27" s="3">
         <v>3100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>11800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>7000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>17400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>18100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>20500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>19400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>14300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>12900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>23200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>6900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>12300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>9400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>5800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>10600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,8 +2175,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2168,8 +2228,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2186,11 +2246,14 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2323,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,8 +2397,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2340,141 +2409,147 @@
         <v>-300</v>
       </c>
       <c r="E32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
         <v>300</v>
       </c>
       <c r="K32" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="L32" s="3">
         <v>-100</v>
       </c>
       <c r="M32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>500</v>
       </c>
       <c r="R32" s="3">
         <v>500</v>
       </c>
       <c r="S32" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E33" s="3">
         <v>3100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>11800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>7000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>17400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>18100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>20500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>19400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>14300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>12900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>23200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-1000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>6900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>12300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>9400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>5800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>10600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2619,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E35" s="3">
         <v>3100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>11800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>7000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>17400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>18100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>20500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>19400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>14300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>12900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>23200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-1000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>6900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>12300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>9400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>5800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>10600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45255</v>
+      </c>
+      <c r="E38" s="2">
         <v>45164</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45073</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44982</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44891</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44800</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44709</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44618</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44528</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44436</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44345</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44254</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44163</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44072</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43981</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43883</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43792</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43701</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43610</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43519</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43428</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43337</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43246</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2802,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,79 +2830,83 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>95800</v>
+      </c>
+      <c r="E41" s="3">
         <v>112600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>116800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>103900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>89400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>72600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>104200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>82200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>70600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>61900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>74400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>84000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>97200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>114600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>95600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>35900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>43000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>45700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>43000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>48000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>40800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>27100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>56500</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2873,10 +2962,10 @@
         <v>0</v>
       </c>
       <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
         <v>6000</v>
-      </c>
-      <c r="V42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W42" s="3" t="s">
         <v>8</v>
@@ -2887,79 +2976,85 @@
       <c r="Y42" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>138200</v>
+      </c>
+      <c r="E43" s="3">
         <v>135100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>142100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>151600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>182700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>183900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>188300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>187700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>182600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>164600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>153600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>119900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>114300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>111000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>129200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>138000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>138700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>130300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>135500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>142000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>147600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>138600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>131200</v>
       </c>
     </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3029,150 +3124,159 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E45" s="3">
         <v>5800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>16000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7800</v>
-      </c>
-      <c r="K45" s="3">
-        <v>6700</v>
       </c>
       <c r="L45" s="3">
         <v>6700</v>
       </c>
       <c r="M45" s="3">
+        <v>6700</v>
+      </c>
+      <c r="N45" s="3">
         <v>7200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>8100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>8000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>8100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>7000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>6800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>242200</v>
+      </c>
+      <c r="E46" s="3">
         <v>253500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>264100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>262600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>278700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>262200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>308500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>277800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>260000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>233300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>235300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>212000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>218600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>231500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>231000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>182000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>189400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>183400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>191700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>198000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>195400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>172500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>194900</v>
       </c>
     </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3242,150 +3346,159 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E48" s="3">
         <v>30000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>31200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>32600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>35200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>36500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>35200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>38100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>40500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>42700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>45200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>49000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>52300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>56200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>57900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>63000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>65100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>66100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>26600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>25700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>23700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>22600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>229500</v>
+      </c>
+      <c r="E49" s="3">
         <v>217200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>218200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>218800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>222800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>223100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>225500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>232800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>234200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>235600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>237000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>237100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>237300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>234800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>234100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>235100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>236400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>242200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>205400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>206700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>207700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>209400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>210500</v>
       </c>
     </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3568,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,79 +3642,85 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E52" s="3">
         <v>21600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>18500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>18400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>13800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,79 +3790,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>524900</v>
+      </c>
+      <c r="E54" s="3">
         <v>522400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>532000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>532300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>550500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>534000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>581500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>559700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>538200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>514600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>520600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>501600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>512000</v>
-      </c>
-      <c r="P54" s="3">
-        <v>529200</v>
       </c>
       <c r="Q54" s="3">
         <v>529200</v>
       </c>
       <c r="R54" s="3">
+        <v>529200</v>
+      </c>
+      <c r="S54" s="3">
         <v>486000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>496400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>496600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>428400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>435100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>431300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>408400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>432700</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3894,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,79 +3922,83 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E57" s="3">
         <v>15700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>16500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>16600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>12900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>17800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>15900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>18100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>16000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>17500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>20300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>15300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>15800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>18600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>20100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>22800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>21600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>22400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>22300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>22000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>23300</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3935,150 +4068,159 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>69200</v>
+      </c>
+      <c r="E59" s="3">
         <v>68200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>82600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>85500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>84400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>78900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>110700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>97900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>83200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>77200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>84900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>85900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>71300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>72800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>79100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>72200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>77900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>66300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>69800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>58900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>63300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>50600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>71200</v>
       </c>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>86800</v>
+      </c>
+      <c r="E60" s="3">
         <v>83900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>97100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>102100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>101000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>91800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>124300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>115600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>99100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>95400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>100900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>103400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>91600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>88100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>94900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>90800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>97900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>89000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>91400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>81300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>85600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>72600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>94500</v>
       </c>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4092,52 +4234,52 @@
         <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>20000</v>
       </c>
       <c r="I61" s="3">
-        <v>54000</v>
+        <v>20000</v>
       </c>
       <c r="J61" s="3">
         <v>54000</v>
       </c>
       <c r="K61" s="3">
+        <v>54000</v>
+      </c>
+      <c r="L61" s="3">
         <v>44000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>33000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>43000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>53000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>68000</v>
-      </c>
-      <c r="P61" s="3">
-        <v>88000</v>
       </c>
       <c r="Q61" s="3">
         <v>88000</v>
       </c>
       <c r="R61" s="3">
+        <v>88000</v>
+      </c>
+      <c r="S61" s="3">
         <v>49000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>54000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>73000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>43000</v>
-      </c>
-      <c r="V61" s="3">
-        <v>58000</v>
       </c>
       <c r="W61" s="3">
         <v>58000</v>
@@ -4146,81 +4288,87 @@
         <v>58000</v>
       </c>
       <c r="Y61" s="3">
+        <v>58000</v>
+      </c>
+      <c r="Z61" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E62" s="3">
         <v>19700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>20400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>23400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>27400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>30300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>30700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>33100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>41500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>45400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>47200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>37600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>45400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>43200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>42600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>43400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>44200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>46200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>11600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>12500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>10300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>9500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4438,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4512,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,79 +4586,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>111300</v>
+      </c>
+      <c r="E66" s="3">
         <v>103500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>117500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>125500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>148400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>142100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>209000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>202700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>184600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>173800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>191100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>194000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>205000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>219200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>225500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>183200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>196100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>208200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>146000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>151800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>153900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>140100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>163800</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4690,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4762,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4836,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4743,8 +4910,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,8 +4984,11 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -4823,70 +4996,73 @@
         <v>85900</v>
       </c>
       <c r="E72" s="3">
+        <v>85900</v>
+      </c>
+      <c r="F72" s="3">
         <v>87600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>80700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>78600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>66100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>52700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>36900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>22200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>375400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>367200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>348700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>352700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>358300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>360500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>361000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>358500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>350700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>350200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>345000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>343800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>337400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>335700</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5132,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5206,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,79 +5280,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>413600</v>
+      </c>
+      <c r="E76" s="3">
         <v>418800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>414500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>406800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>402100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>392000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>372400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>357000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>353600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>340800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>329500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>307600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>306900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>309900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>303700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>302800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>300300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>288400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>282400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>283300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>277400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>268300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>268800</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5428,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45255</v>
+      </c>
+      <c r="E80" s="2">
         <v>45164</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45073</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44982</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44891</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44800</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44709</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44618</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44528</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44436</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44345</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44254</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44163</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44072</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43981</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43883</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43792</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43701</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43610</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43519</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43428</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43337</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43246</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E81" s="3">
         <v>3100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>11800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>7000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>17400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>18100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>20500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>19400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>14300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>12900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>23200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-1000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>6900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>12300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>9400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>5800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>10600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,13 +5611,14 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="E83" s="3">
         <v>2200</v>
@@ -5429,64 +5627,67 @@
         <v>2200</v>
       </c>
       <c r="G83" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="H83" s="3">
         <v>2100</v>
       </c>
       <c r="I83" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="J83" s="3">
         <v>2200</v>
       </c>
       <c r="K83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="L83" s="3">
         <v>2100</v>
-      </c>
-      <c r="L83" s="3">
-        <v>2000</v>
       </c>
       <c r="M83" s="3">
         <v>2000</v>
       </c>
       <c r="N83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="O83" s="3">
         <v>2200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2500</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>2700</v>
       </c>
       <c r="R83" s="3">
         <v>2700</v>
       </c>
       <c r="S83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="T83" s="3">
         <v>2900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2200</v>
-      </c>
-      <c r="V83" s="3">
-        <v>2100</v>
       </c>
       <c r="W83" s="3">
         <v>2100</v>
       </c>
       <c r="X83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="Y83" s="3">
         <v>2000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5757,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5831,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5905,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5979,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,79 +6053,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-2200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>17800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>40200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>29000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>26800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>19200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>11000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>18600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>28000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>20300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-3000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>30100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>11800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>18300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-16600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,37 +6157,38 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-700</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-300</v>
       </c>
       <c r="J91" s="3">
         <v>-300</v>
       </c>
       <c r="K91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L91" s="3">
         <v>-1300</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-1000</v>
       </c>
       <c r="M91" s="3">
         <v>-1000</v>
@@ -5977,40 +6197,43 @@
         <v>-1000</v>
       </c>
       <c r="O91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="P91" s="3">
         <v>-1500</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-300</v>
       </c>
       <c r="Q91" s="3">
         <v>-300</v>
       </c>
       <c r="R91" s="3">
-        <v>-800</v>
+        <v>-300</v>
       </c>
       <c r="S91" s="3">
         <v>-800</v>
       </c>
       <c r="T91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="U91" s="3">
         <v>-500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6303,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,79 +6377,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>2400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>2300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1300</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-1000</v>
       </c>
       <c r="M94" s="3">
         <v>-1000</v>
       </c>
       <c r="N94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="O94" s="3">
         <v>-1200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-24800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-6900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,8 +6481,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6267,16 +6500,16 @@
         <v>-4700</v>
       </c>
       <c r="H96" s="3">
-        <v>-4600</v>
+        <v>-4700</v>
       </c>
       <c r="I96" s="3">
         <v>-4600</v>
       </c>
       <c r="J96" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="K96" s="3">
         <v>-4700</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-4600</v>
       </c>
       <c r="L96" s="3">
         <v>-4600</v>
@@ -6288,7 +6521,7 @@
         <v>-4600</v>
       </c>
       <c r="O96" s="3">
-        <v>-4500</v>
+        <v>-4600</v>
       </c>
       <c r="P96" s="3">
         <v>-4500</v>
@@ -6303,7 +6536,7 @@
         <v>-4500</v>
       </c>
       <c r="T96" s="3">
-        <v>-4100</v>
+        <v>-4500</v>
       </c>
       <c r="U96" s="3">
         <v>-4100</v>
@@ -6315,13 +6548,16 @@
         <v>-4100</v>
       </c>
       <c r="X96" s="3">
-        <v>-3800</v>
+        <v>-4100</v>
       </c>
       <c r="Y96" s="3">
         <v>-3800</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>-3800</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6627,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6701,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,217 +6775,229 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-7600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-25900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-9300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-29100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>8100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-11400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-13500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-16900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-27600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>32700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-10300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-22300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>30700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-28000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-2300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-1600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-11700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-4800</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>-200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-16800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>12900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>14500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>16900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-31600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>22300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>11600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>8700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-12500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-9600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-13200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-17400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>18900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>59700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-7100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-2700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>7100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>13800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-29400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>13300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RGP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RGP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
   <si>
     <t>RGP</t>
   </si>
@@ -656,339 +656,352 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45346</v>
+      </c>
+      <c r="E7" s="2">
         <v>45255</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45164</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45073</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44982</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44891</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44800</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44709</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44618</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44528</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44436</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44345</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44254</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44163</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44072</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43981</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43883</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43792</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43701</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43610</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43519</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43428</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43337</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43246</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>151300</v>
+      </c>
+      <c r="E8" s="3">
         <v>163100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>170200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>184400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>186800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>200400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>204100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>217000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>204600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>200200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>183100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>172300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>156600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>153200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>147300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>178600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>168100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>184500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>172200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>182100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>179500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>188800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>178600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>183800</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>95300</v>
+      </c>
+      <c r="E9" s="3">
         <v>99700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>103200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>108700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>115200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>118000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>120600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>127400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>127800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>121500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>111700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>104000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>99600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>95000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>89400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>106400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>106600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>110100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>104700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>109200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>111600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>115400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>110400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>113400</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E10" s="3">
         <v>63400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>67000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>75700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>71600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>82400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>83500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>89600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>76800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>78700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>71400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>68300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>57000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>58200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>57900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>72200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>61500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>74400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>67500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>72900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>67900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>73400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>68200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>70400</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1015,8 +1028,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1089,8 +1103,11 @@
       <c r="Z12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1163,67 +1180,70 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E14" s="3">
         <v>2300</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2900</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>-400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>6600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-900</v>
-      </c>
-      <c r="T14" s="3">
-        <v>-100</v>
       </c>
       <c r="U14" s="3">
         <v>-100</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
+      <c r="V14" s="3">
+        <v>-100</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
@@ -1234,19 +1254,22 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E15" s="3">
         <v>2100</v>
-      </c>
-      <c r="E15" s="3">
-        <v>2200</v>
       </c>
       <c r="F15" s="3">
         <v>2200</v>
@@ -1255,64 +1278,67 @@
         <v>2200</v>
       </c>
       <c r="H15" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="I15" s="3">
         <v>2100</v>
       </c>
       <c r="J15" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="K15" s="3">
         <v>2200</v>
       </c>
       <c r="L15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="M15" s="3">
         <v>2100</v>
-      </c>
-      <c r="M15" s="3">
-        <v>2000</v>
       </c>
       <c r="N15" s="3">
         <v>2000</v>
       </c>
       <c r="O15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P15" s="3">
         <v>2200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2500</v>
-      </c>
-      <c r="R15" s="3">
-        <v>2700</v>
       </c>
       <c r="S15" s="3">
         <v>2700</v>
       </c>
       <c r="T15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="U15" s="3">
         <v>2900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>2200</v>
-      </c>
-      <c r="W15" s="3">
-        <v>2100</v>
       </c>
       <c r="X15" s="3">
         <v>2100</v>
       </c>
       <c r="Y15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="Z15" s="3">
         <v>2000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1336,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>147000</v>
+      </c>
+      <c r="E17" s="3">
         <v>154800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>165300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>167400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>179700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>176900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>178900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>188900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>187100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>180500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>165100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>156900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>154600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>152000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>143100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>171100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>164600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>166800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>164200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>168300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>169300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>172500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>168800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>174300</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E18" s="3">
         <v>8300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>17000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>23500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>25200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>28100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>17500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>19700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>18000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>15400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>4200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>17700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>8000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>13800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>10200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>16300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>9800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1512,156 +1545,163 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E20" s="3">
         <v>300</v>
       </c>
       <c r="F20" s="3">
+        <v>300</v>
+      </c>
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-200</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>-300</v>
       </c>
       <c r="L20" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="M20" s="3">
         <v>100</v>
       </c>
       <c r="N20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-300</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>100</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-500</v>
       </c>
       <c r="S20" s="3">
         <v>-500</v>
       </c>
       <c r="T20" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E21" s="3">
         <v>10800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>7400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>19300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>9200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>25400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>27300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>29900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>19400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>21900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>20100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>17500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>6800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>9700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>5600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>20600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>10000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>16200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>12400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>18500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>11900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1701,8 +1741,8 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>8</v>
+      <c r="P22" s="3">
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>8</v>
@@ -1719,14 +1759,14 @@
       <c r="U22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W22" s="3">
         <v>600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>700</v>
-      </c>
-      <c r="X22" s="3">
-        <v>600</v>
       </c>
       <c r="Y22" s="3">
         <v>600</v>
@@ -1734,156 +1774,165 @@
       <c r="Z22" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E23" s="3">
         <v>8600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>17200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>23300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>25100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>27800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>17200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>19900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>18100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>15400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>17700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>7600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>13400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>9600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>15700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>9200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E24" s="3">
         <v>3800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5400</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>5900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-2200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-7800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-4000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>4000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1956,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E26" s="3">
         <v>4900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>11800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>7000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>17400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>18100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>20500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>19400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>14300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>12900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>23200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>6900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>12300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>9400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>5800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>10600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>5700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E27" s="3">
         <v>4900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>11800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>7000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>17400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>18100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>20500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>19400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>14300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>12900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>23200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>6900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>12300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>9400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>5800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>10600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>5700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2178,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2231,8 +2292,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2249,11 +2310,14 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2326,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2400,156 +2467,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="E32" s="3">
         <v>-300</v>
       </c>
       <c r="F32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>200</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>300</v>
       </c>
       <c r="L32" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="M32" s="3">
         <v>-100</v>
       </c>
       <c r="N32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>300</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
-      </c>
-      <c r="R32" s="3">
-        <v>500</v>
       </c>
       <c r="S32" s="3">
         <v>500</v>
       </c>
       <c r="T32" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E33" s="3">
         <v>4900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>11800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>7000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>17400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>18100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>20500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>19400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>14300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>12900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>23200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>6900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>12300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>9400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>5800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>10600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>5700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2622,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E35" s="3">
         <v>4900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>11800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>7000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>17400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>18100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>20500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>19400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>14300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>12900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>23200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>6900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>12300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>9400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>5800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>10600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>5700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45346</v>
+      </c>
+      <c r="E38" s="2">
         <v>45255</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45164</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45073</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44982</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44891</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44800</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44709</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44618</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44528</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44436</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44345</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44254</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44163</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44072</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43981</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43883</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43792</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43701</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43610</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43519</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43428</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43337</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43246</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2803,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2831,82 +2917,86 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>113800</v>
+      </c>
+      <c r="E41" s="3">
         <v>95800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>112600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>116800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>103900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>89400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>72600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>104200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>82200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>70600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>61900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>74400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>84000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>97200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>114600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>95600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>35900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>43000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>45700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>43000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>48000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>40800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>27100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>56500</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2965,10 +3055,10 @@
         <v>0</v>
       </c>
       <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
         <v>6000</v>
-      </c>
-      <c r="W42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X42" s="3" t="s">
         <v>8</v>
@@ -2979,82 +3069,88 @@
       <c r="Z42" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>120200</v>
+      </c>
+      <c r="E43" s="3">
         <v>138200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>135100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>142100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>151600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>182700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>183900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>188300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>187700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>182600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>164600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>153600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>119900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>114300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>111000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>129200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>138000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>138700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>130300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>135500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>142000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>147600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>138600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>131200</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3127,156 +3223,165 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E45" s="3">
         <v>8200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>5800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>16000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7800</v>
-      </c>
-      <c r="L45" s="3">
-        <v>6700</v>
       </c>
       <c r="M45" s="3">
         <v>6700</v>
       </c>
       <c r="N45" s="3">
+        <v>6700</v>
+      </c>
+      <c r="O45" s="3">
         <v>7200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>8100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>8000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>8100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>6800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>251300</v>
+      </c>
+      <c r="E46" s="3">
         <v>242200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>253500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>264100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>262600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>278700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>262200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>308500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>277800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>260000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>233300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>235300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>212000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>218600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>231500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>231000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>182000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>189400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>183400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>191700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>198000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>195400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>172500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>194900</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3349,156 +3454,165 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E48" s="3">
         <v>28600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>30000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>31200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>32600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>35200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>36500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>35200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>38100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>40500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>42700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>45200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>49000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>52300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>56200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>57900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>63000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>65100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>66100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>26600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>25700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>23700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>22600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>227900</v>
+      </c>
+      <c r="E49" s="3">
         <v>229500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>217200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>218200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>218800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>222800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>223100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>225500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>232800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>234200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>235600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>237000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>237100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>237300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>234800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>234100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>235100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>236400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>242200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>205400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>206700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>207700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>209400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>210500</v>
       </c>
     </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3571,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3645,82 +3762,88 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E52" s="3">
         <v>24600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>21600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>18500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>18400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>13800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>12200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3793,82 +3916,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>523200</v>
+      </c>
+      <c r="E54" s="3">
         <v>524900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>522400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>532000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>532300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>550500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>534000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>581500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>559700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>538200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>514600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>520600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>501600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>512000</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>529200</v>
       </c>
       <c r="R54" s="3">
         <v>529200</v>
       </c>
       <c r="S54" s="3">
+        <v>529200</v>
+      </c>
+      <c r="T54" s="3">
         <v>486000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>496400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>496600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>428400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>435100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>431300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>408400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>432700</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3895,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3923,82 +4053,86 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E57" s="3">
         <v>17500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>16500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>16600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>12900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>17800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>15900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>18100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>16000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>17500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>20300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>15300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>15800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>18600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>20100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>22800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>21600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>22400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>22300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>22000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>23300</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4071,156 +4205,165 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>66800</v>
+      </c>
+      <c r="E59" s="3">
         <v>69200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>68200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>82600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>85500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>84400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>78900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>110700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>97900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>83200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>77200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>84900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>85900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>71300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>72800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>79100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>72200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>77900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>66300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>69800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>58900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>63300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>50600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>71200</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>84100</v>
+      </c>
+      <c r="E60" s="3">
         <v>86800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>83900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>97100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>102100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>101000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>91800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>124300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>115600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>99100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>95400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>100900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>103400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>91600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>88100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>94900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>90800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>97900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>89000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>91400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>81300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>85600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>72600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>94500</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4237,52 +4380,52 @@
         <v>0</v>
       </c>
       <c r="H61" s="3">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
         <v>20000</v>
       </c>
       <c r="J61" s="3">
-        <v>54000</v>
+        <v>20000</v>
       </c>
       <c r="K61" s="3">
         <v>54000</v>
       </c>
       <c r="L61" s="3">
+        <v>54000</v>
+      </c>
+      <c r="M61" s="3">
         <v>44000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>33000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>43000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>53000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>68000</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>88000</v>
       </c>
       <c r="R61" s="3">
         <v>88000</v>
       </c>
       <c r="S61" s="3">
+        <v>88000</v>
+      </c>
+      <c r="T61" s="3">
         <v>49000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>54000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>73000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>43000</v>
-      </c>
-      <c r="W61" s="3">
-        <v>58000</v>
       </c>
       <c r="X61" s="3">
         <v>58000</v>
@@ -4291,84 +4434,90 @@
         <v>58000</v>
       </c>
       <c r="Z61" s="3">
+        <v>58000</v>
+      </c>
+      <c r="AA61" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E62" s="3">
         <v>24500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>19700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>20400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>23400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>27400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>30300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>30700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>33100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>41500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>45400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>47200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>37600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>45400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>43200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>42600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>43400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>44200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>46200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>11600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>12500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>10300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>9500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4441,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4515,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4589,82 +4744,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>108300</v>
+      </c>
+      <c r="E66" s="3">
         <v>111300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>103500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>117500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>125500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>148400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>142100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>209000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>202700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>184600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>173800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>191100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>194000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>205000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>219200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>225500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>183200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>196100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>208200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>146000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>151800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>153900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>140100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>163800</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4691,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4765,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4839,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4913,8 +5081,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4987,82 +5158,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>85900</v>
+        <v>83000</v>
       </c>
       <c r="E72" s="3">
         <v>85900</v>
       </c>
       <c r="F72" s="3">
+        <v>85900</v>
+      </c>
+      <c r="G72" s="3">
         <v>87600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>80700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>78600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>66100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>52700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>36900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>22200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>375400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>367200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>348700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>352700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>358300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>360500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>361000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>358500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>350700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>350200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>345000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>343800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>337400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>335700</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5135,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5209,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5283,82 +5466,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>414900</v>
+      </c>
+      <c r="E76" s="3">
         <v>413600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>418800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>414500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>406800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>402100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>392000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>372400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>357000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>353600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>340800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>329500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>307600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>306900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>309900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>303700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>302800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>300300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>288400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>282400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>283300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>277400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>268300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>268800</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5431,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45346</v>
+      </c>
+      <c r="E80" s="2">
         <v>45255</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45164</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45073</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44982</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44891</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44800</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44709</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44618</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44528</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44436</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44345</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44254</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44163</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44072</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43981</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43883</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43792</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43701</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43610</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43519</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43428</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43337</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43246</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E81" s="3">
         <v>4900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>11800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>7000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>17400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>18100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>20500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>19400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>14300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>12900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>23200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>6900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>12300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>9400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>5800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>10600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>5700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5612,16 +5810,17 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E83" s="3">
         <v>2100</v>
-      </c>
-      <c r="E83" s="3">
-        <v>2200</v>
       </c>
       <c r="F83" s="3">
         <v>2200</v>
@@ -5630,64 +5829,67 @@
         <v>2200</v>
       </c>
       <c r="H83" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="I83" s="3">
         <v>2100</v>
       </c>
       <c r="J83" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="K83" s="3">
         <v>2200</v>
       </c>
       <c r="L83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="M83" s="3">
         <v>2100</v>
-      </c>
-      <c r="M83" s="3">
-        <v>2000</v>
       </c>
       <c r="N83" s="3">
         <v>2000</v>
       </c>
       <c r="O83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="P83" s="3">
         <v>2200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2500</v>
-      </c>
-      <c r="R83" s="3">
-        <v>2700</v>
       </c>
       <c r="S83" s="3">
         <v>2700</v>
       </c>
       <c r="T83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="U83" s="3">
         <v>2900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2200</v>
-      </c>
-      <c r="W83" s="3">
-        <v>2100</v>
       </c>
       <c r="X83" s="3">
         <v>2100</v>
       </c>
       <c r="Y83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="Z83" s="3">
         <v>2000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5760,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5834,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5908,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5982,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6056,82 +6270,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E89" s="3">
         <v>500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>17800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>40200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>29000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>26800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>19200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>11000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>18600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>28000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>20300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-3000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>30100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>11800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>18300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-16600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6158,40 +6378,41 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-700</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-300</v>
       </c>
       <c r="K91" s="3">
         <v>-300</v>
       </c>
       <c r="L91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M91" s="3">
         <v>-1300</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-1000</v>
       </c>
       <c r="N91" s="3">
         <v>-1000</v>
@@ -6200,40 +6421,43 @@
         <v>-1000</v>
       </c>
       <c r="P91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-1500</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-300</v>
       </c>
       <c r="R91" s="3">
         <v>-300</v>
       </c>
       <c r="S91" s="3">
-        <v>-800</v>
+        <v>-300</v>
       </c>
       <c r="T91" s="3">
         <v>-800</v>
       </c>
       <c r="U91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="V91" s="3">
         <v>-500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-2500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6306,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6380,82 +6607,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>2400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>2300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1300</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-1000</v>
       </c>
       <c r="N94" s="3">
         <v>-1000</v>
       </c>
       <c r="O94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="P94" s="3">
         <v>-1200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-24800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-6900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6482,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6503,16 +6737,16 @@
         <v>-4700</v>
       </c>
       <c r="I96" s="3">
-        <v>-4600</v>
+        <v>-4700</v>
       </c>
       <c r="J96" s="3">
         <v>-4600</v>
       </c>
       <c r="K96" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="L96" s="3">
         <v>-4700</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-4600</v>
       </c>
       <c r="M96" s="3">
         <v>-4600</v>
@@ -6524,7 +6758,7 @@
         <v>-4600</v>
       </c>
       <c r="P96" s="3">
-        <v>-4500</v>
+        <v>-4600</v>
       </c>
       <c r="Q96" s="3">
         <v>-4500</v>
@@ -6539,7 +6773,7 @@
         <v>-4500</v>
       </c>
       <c r="U96" s="3">
-        <v>-4100</v>
+        <v>-4500</v>
       </c>
       <c r="V96" s="3">
         <v>-4100</v>
@@ -6551,13 +6785,16 @@
         <v>-4100</v>
       </c>
       <c r="Y96" s="3">
-        <v>-3800</v>
+        <v>-4100</v>
       </c>
       <c r="Z96" s="3">
         <v>-3800</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>-3800</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6630,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6704,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6778,226 +7021,238 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-9700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-7600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-25900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-9300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-29100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-7100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>8100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-11400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-13500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-16900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-27600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>32700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-10300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-22300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>30700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-28000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-2300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-11700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-4800</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-100</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>-200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-16800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>12900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>14500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>16900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-31600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>22300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>11600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>8700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-12500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-9600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-13200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-17400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>18900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>59700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-7100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-4900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>7100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>13800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-29400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>13300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RGP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RGP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>RGP</t>
   </si>
@@ -656,352 +656,365 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45437</v>
+      </c>
+      <c r="E7" s="2">
         <v>45346</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45255</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45164</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45073</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44982</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44891</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44800</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44709</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44618</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44528</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44436</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44345</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44254</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44163</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44072</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43981</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43883</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43792</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43701</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43610</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43519</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43428</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43337</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43246</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>148200</v>
+      </c>
+      <c r="E8" s="3">
         <v>151300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>163100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>170200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>184400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>186800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>200400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>204100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>217000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>204600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>200200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>183100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>172300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>156600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>153200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>147300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>178600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>168100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>184500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>172200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>182100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>179500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>188800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>178600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>183800</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>88600</v>
+      </c>
+      <c r="E9" s="3">
         <v>95300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>99700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>103200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>108700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>115200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>118000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>120600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>127400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>127800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>121500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>111700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>104000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>99600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>95000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>89400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>106400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>106600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>110100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>104700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>109200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>111600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>115400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>110400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>113400</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>59600</v>
+      </c>
+      <c r="E10" s="3">
         <v>56000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>63400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>67000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>75700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>71600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>82400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>83500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>89600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>76800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>78700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>71400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>68300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>57000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>58200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>57900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>72200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>61500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>74400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>67500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>72900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>67900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>73400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>68200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>70400</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1029,8 +1042,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1106,8 +1120,11 @@
       <c r="AA12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1183,70 +1200,73 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E14" s="3">
         <v>1600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2300</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2900</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>-400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>6600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-900</v>
-      </c>
-      <c r="U14" s="3">
-        <v>-100</v>
       </c>
       <c r="V14" s="3">
         <v>-100</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
+      <c r="W14" s="3">
+        <v>-100</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
@@ -1257,22 +1277,25 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E15" s="3">
         <v>2200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2100</v>
-      </c>
-      <c r="F15" s="3">
-        <v>2200</v>
       </c>
       <c r="G15" s="3">
         <v>2200</v>
@@ -1281,64 +1304,67 @@
         <v>2200</v>
       </c>
       <c r="I15" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="J15" s="3">
         <v>2100</v>
       </c>
       <c r="K15" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="L15" s="3">
         <v>2200</v>
       </c>
       <c r="M15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="N15" s="3">
         <v>2100</v>
-      </c>
-      <c r="N15" s="3">
-        <v>2000</v>
       </c>
       <c r="O15" s="3">
         <v>2000</v>
       </c>
       <c r="P15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Q15" s="3">
         <v>2200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>2400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2500</v>
-      </c>
-      <c r="S15" s="3">
-        <v>2700</v>
       </c>
       <c r="T15" s="3">
         <v>2700</v>
       </c>
       <c r="U15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="V15" s="3">
         <v>2900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>2500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2200</v>
-      </c>
-      <c r="X15" s="3">
-        <v>2100</v>
       </c>
       <c r="Y15" s="3">
         <v>2100</v>
       </c>
       <c r="Z15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AA15" s="3">
         <v>2000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>136900</v>
+      </c>
+      <c r="E17" s="3">
         <v>147000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>154800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>165300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>167400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>179700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>176900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>178900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>188900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>187100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>180500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>165100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>156900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>154600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>152000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>143100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>171100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>164600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>166800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>164200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>168300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>169300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>172500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>168800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>174300</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E18" s="3">
         <v>4300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>8300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>17000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>7100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>23500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>25200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>28100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>17500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>19700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>18000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>15400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>4200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>7500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>17700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>8000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>13800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>10200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>16300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>9800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,8 +1579,9 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1555,153 +1589,159 @@
         <v>200</v>
       </c>
       <c r="E20" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F20" s="3">
         <v>300</v>
       </c>
       <c r="G20" s="3">
+        <v>300</v>
+      </c>
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3">
         <v>-300</v>
       </c>
       <c r="M20" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="N20" s="3">
         <v>100</v>
       </c>
       <c r="O20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-300</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
-      </c>
-      <c r="S20" s="3">
-        <v>-500</v>
       </c>
       <c r="T20" s="3">
         <v>-500</v>
       </c>
       <c r="U20" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
       <c r="Z20" s="3">
         <v>0</v>
       </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E21" s="3">
         <v>6600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>10800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>7400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>19300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>9200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>25400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>27300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>29900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>19400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>21900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>20100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>17500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>3900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>6800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>9700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>20600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>10000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>16200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>12400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>18500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>11900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1744,8 +1784,8 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>8</v>
+      <c r="Q22" s="3">
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>8</v>
@@ -1762,14 +1802,14 @@
       <c r="V22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X22" s="3">
         <v>600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>700</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>600</v>
       </c>
       <c r="Z22" s="3">
         <v>600</v>
@@ -1777,162 +1817,171 @@
       <c r="AA22" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E23" s="3">
         <v>4500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>8600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>17200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>23300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>25100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>27800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>17200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>19900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>18100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>15400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>4200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>3000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>17700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>7600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>13400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>9600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>15700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>9200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5400</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>5900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>7000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-2200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-7800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>1100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-4000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>3500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E26" s="3">
         <v>2600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>11800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>17400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>18100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>20500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>19400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>14300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>12900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>23200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-1000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>6900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>12300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>9400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>5800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>10600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>5700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E27" s="3">
         <v>2600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>11800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>7000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>17400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>18100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>20500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>14300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>12900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>23200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>6900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>12300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>9400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>5800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>10600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>5700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2295,8 +2356,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2313,11 +2374,14 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,8 +2537,11 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2479,153 +2549,159 @@
         <v>-200</v>
       </c>
       <c r="E32" s="3">
-        <v>-300</v>
+        <v>-200</v>
       </c>
       <c r="F32" s="3">
         <v>-300</v>
       </c>
       <c r="G32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="L32" s="3">
         <v>300</v>
       </c>
       <c r="M32" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="N32" s="3">
         <v>-100</v>
       </c>
       <c r="O32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>300</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
-      </c>
-      <c r="S32" s="3">
-        <v>500</v>
       </c>
       <c r="T32" s="3">
         <v>500</v>
       </c>
       <c r="U32" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E33" s="3">
         <v>2600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>11800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>7000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>17400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>18100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>20500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>14300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>12900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>23200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-1000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>6900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>12300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>9400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>5800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>10600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>5700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E35" s="3">
         <v>2600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>11800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>7000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>17400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>18100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>20500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>14300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>12900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>23200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-1000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>6900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>12300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>9400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>5800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>10600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>5700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45437</v>
+      </c>
+      <c r="E38" s="2">
         <v>45346</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45255</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45164</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45073</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44982</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44891</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44800</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44709</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44618</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44528</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44436</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44345</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44254</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44163</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44072</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43981</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43883</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43792</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43701</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43610</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43519</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43428</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43337</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43246</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,85 +3004,89 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>108900</v>
+      </c>
+      <c r="E41" s="3">
         <v>113800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>95800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>112600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>116800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>103900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>89400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>72600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>104200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>82200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>70600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>61900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>74400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>84000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>97200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>114600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>95600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>35900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>43000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>45700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>43000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>48000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>40800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>27100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>56500</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3058,10 +3148,10 @@
         <v>0</v>
       </c>
       <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
         <v>6000</v>
-      </c>
-      <c r="X42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y42" s="3" t="s">
         <v>8</v>
@@ -3072,85 +3162,91 @@
       <c r="AA42" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>116100</v>
+      </c>
+      <c r="E43" s="3">
         <v>120200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>138200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>135100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>142100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>151600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>182700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>183900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>188300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>187700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>182600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>164600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>153600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>119900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>114300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>111000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>129200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>138000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>138700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>130300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>135500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>142000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>147600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>138600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>131200</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3226,162 +3322,171 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E45" s="3">
         <v>17300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>6600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>16000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7800</v>
-      </c>
-      <c r="M45" s="3">
-        <v>6700</v>
       </c>
       <c r="N45" s="3">
         <v>6700</v>
       </c>
       <c r="O45" s="3">
+        <v>6700</v>
+      </c>
+      <c r="P45" s="3">
         <v>7200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>8100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>8000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>7100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>8100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>6800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>240800</v>
+      </c>
+      <c r="E46" s="3">
         <v>251300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>242200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>253500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>264100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>262600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>278700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>262200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>308500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>277800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>260000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>233300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>235300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>212000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>218600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>231500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>231000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>182000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>189400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>183400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>191700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>198000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>195400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>172500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>194900</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3457,162 +3562,171 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15700</v>
+      </c>
+      <c r="E48" s="3">
         <v>17500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>28600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>30000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>31200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>32600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>35200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>36500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>35200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>38100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>40500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>42700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>45200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>49000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>52300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>56200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>57900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>63000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>65100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>66100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>26600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>25700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>23700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>22600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>226200</v>
+      </c>
+      <c r="E49" s="3">
         <v>227900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>229500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>217200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>218200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>218800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>222800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>223100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>225500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>232800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>234200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>235600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>237000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>237100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>237300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>234800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>234100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>235100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>236400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>242200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>205400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>206700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>207700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>209400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>210500</v>
       </c>
     </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,85 +3882,91 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>28300</v>
+      </c>
+      <c r="E52" s="3">
         <v>26500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>24600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>21600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>18500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>18400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>13800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>12300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,85 +4042,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>510900</v>
+      </c>
+      <c r="E54" s="3">
         <v>523200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>524900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>522400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>532000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>532300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>550500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>534000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>581500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>559700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>538200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>514600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>520600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>501600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>512000</v>
-      </c>
-      <c r="R54" s="3">
-        <v>529200</v>
       </c>
       <c r="S54" s="3">
         <v>529200</v>
       </c>
       <c r="T54" s="3">
+        <v>529200</v>
+      </c>
+      <c r="U54" s="3">
         <v>486000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>496400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>496600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>428400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>435100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>431300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>408400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>432700</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,85 +4184,89 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E57" s="3">
         <v>17400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>17500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>16500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>16600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>12900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>13600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>17800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>15900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>18100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>16000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>17500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>20300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>15300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>15800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>18600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>20100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>22800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>21600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>22400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>22300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>22000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>23300</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4208,162 +4342,171 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>57200</v>
+      </c>
+      <c r="E59" s="3">
         <v>66800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>69200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>68200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>82600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>85500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>84400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>78900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>110700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>97900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>83200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>77200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>84900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>85900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>71300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>72800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>79100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>72200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>77900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>66300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>69800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>58900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>63300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>50600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>71200</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>72400</v>
+      </c>
+      <c r="E60" s="3">
         <v>84100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>86800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>83900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>97100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>102100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>101000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>91800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>124300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>115600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>99100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>95400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>100900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>103400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>91600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>88100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>94900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>90800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>97900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>89000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>91400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>81300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>85600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>72600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>94500</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4383,52 +4526,52 @@
         <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>20000</v>
       </c>
       <c r="K61" s="3">
-        <v>54000</v>
+        <v>20000</v>
       </c>
       <c r="L61" s="3">
         <v>54000</v>
       </c>
       <c r="M61" s="3">
+        <v>54000</v>
+      </c>
+      <c r="N61" s="3">
         <v>44000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>33000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>43000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>53000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>68000</v>
-      </c>
-      <c r="R61" s="3">
-        <v>88000</v>
       </c>
       <c r="S61" s="3">
         <v>88000</v>
       </c>
       <c r="T61" s="3">
+        <v>88000</v>
+      </c>
+      <c r="U61" s="3">
         <v>49000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>54000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>73000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>43000</v>
-      </c>
-      <c r="X61" s="3">
-        <v>58000</v>
       </c>
       <c r="Y61" s="3">
         <v>58000</v>
@@ -4437,87 +4580,93 @@
         <v>58000</v>
       </c>
       <c r="AA61" s="3">
+        <v>58000</v>
+      </c>
+      <c r="AB61" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>19700</v>
+      </c>
+      <c r="E62" s="3">
         <v>24200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>24500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>19700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>20400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>23400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>27400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>30300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>30700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>33100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>41500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>45400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>47200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>37600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>45400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>43200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>42600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>43400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>44200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>46200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>11600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>12500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>10300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>9500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,85 +4902,91 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>92200</v>
+      </c>
+      <c r="E66" s="3">
         <v>108300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>111300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>103500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>117500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>125500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>148400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>142100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>209000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>202700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>184600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>173800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>191100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>194000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>205000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>219200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>225500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>183200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>196100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>208200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>146000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>151800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>153900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>140100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>163800</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5084,8 +5252,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,85 +5332,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>88600</v>
+      </c>
+      <c r="E72" s="3">
         <v>83000</v>
-      </c>
-      <c r="E72" s="3">
-        <v>85900</v>
       </c>
       <c r="F72" s="3">
         <v>85900</v>
       </c>
       <c r="G72" s="3">
+        <v>85900</v>
+      </c>
+      <c r="H72" s="3">
         <v>87600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>80700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>78600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>66100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>52700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>36900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>22200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>375400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>367200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>348700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>352700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>358300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>360500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>361000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>358500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>350700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>350200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>345000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>343800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>337400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>335700</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,85 +5652,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>418800</v>
+      </c>
+      <c r="E76" s="3">
         <v>414900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>413600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>418800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>414500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>406800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>402100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>392000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>372400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>357000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>353600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>340800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>329500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>307600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>306900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>309900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>303700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>302800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>300300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>288400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>282400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>283300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>277400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>268300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>268800</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45437</v>
+      </c>
+      <c r="E80" s="2">
         <v>45346</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45255</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45164</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45073</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44982</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44891</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44800</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44709</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44618</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44528</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44436</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44345</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44254</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44163</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44072</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43981</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43883</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43792</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43701</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43610</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43519</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43428</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43337</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43246</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E81" s="3">
         <v>2600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>11800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>7000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>17400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>18100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>20500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>14300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>12900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>23200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-1000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>6900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>12300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>9400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>5800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>10600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>5700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,19 +6009,20 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E83" s="3">
         <v>2200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2100</v>
-      </c>
-      <c r="F83" s="3">
-        <v>2200</v>
       </c>
       <c r="G83" s="3">
         <v>2200</v>
@@ -5832,64 +6031,67 @@
         <v>2200</v>
       </c>
       <c r="I83" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="J83" s="3">
         <v>2100</v>
       </c>
       <c r="K83" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="L83" s="3">
         <v>2200</v>
       </c>
       <c r="M83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="N83" s="3">
         <v>2100</v>
-      </c>
-      <c r="N83" s="3">
-        <v>2000</v>
       </c>
       <c r="O83" s="3">
         <v>2000</v>
       </c>
       <c r="P83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="Q83" s="3">
         <v>2200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2500</v>
-      </c>
-      <c r="S83" s="3">
-        <v>2700</v>
       </c>
       <c r="T83" s="3">
         <v>2700</v>
       </c>
       <c r="U83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="V83" s="3">
         <v>2900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2200</v>
-      </c>
-      <c r="X83" s="3">
-        <v>2100</v>
       </c>
       <c r="Y83" s="3">
         <v>2100</v>
       </c>
       <c r="Z83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AA83" s="3">
         <v>2000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,85 +6487,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E89" s="3">
         <v>20500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>17800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>40200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>29000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>26800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>19200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>3000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>11000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>18600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>28000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>4300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>20300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-3000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>30100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>11800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>18300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-16600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,8 +6599,9 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -6388,34 +6609,34 @@
         <v>-100</v>
       </c>
       <c r="E91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-700</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-300</v>
       </c>
       <c r="L91" s="3">
         <v>-300</v>
       </c>
       <c r="M91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N91" s="3">
         <v>-1300</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-1000</v>
       </c>
       <c r="O91" s="3">
         <v>-1000</v>
@@ -6424,40 +6645,43 @@
         <v>-1000</v>
       </c>
       <c r="Q91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="R91" s="3">
         <v>-1500</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-300</v>
       </c>
       <c r="S91" s="3">
         <v>-300</v>
       </c>
       <c r="T91" s="3">
-        <v>-800</v>
+        <v>-300</v>
       </c>
       <c r="U91" s="3">
         <v>-800</v>
       </c>
       <c r="V91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="W91" s="3">
         <v>-500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,85 +6837,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>2400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>2300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1300</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-1000</v>
       </c>
       <c r="O94" s="3">
         <v>-1000</v>
       </c>
       <c r="P94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-24800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-6900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,8 +6949,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6740,16 +6974,16 @@
         <v>-4700</v>
       </c>
       <c r="J96" s="3">
-        <v>-4600</v>
+        <v>-4700</v>
       </c>
       <c r="K96" s="3">
         <v>-4600</v>
       </c>
       <c r="L96" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="M96" s="3">
         <v>-4700</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-4600</v>
       </c>
       <c r="N96" s="3">
         <v>-4600</v>
@@ -6761,7 +6995,7 @@
         <v>-4600</v>
       </c>
       <c r="Q96" s="3">
-        <v>-4500</v>
+        <v>-4600</v>
       </c>
       <c r="R96" s="3">
         <v>-4500</v>
@@ -6776,7 +7010,7 @@
         <v>-4500</v>
       </c>
       <c r="V96" s="3">
-        <v>-4100</v>
+        <v>-4500</v>
       </c>
       <c r="W96" s="3">
         <v>-4100</v>
@@ -6788,13 +7022,16 @@
         <v>-4100</v>
       </c>
       <c r="Z96" s="3">
-        <v>-3800</v>
+        <v>-4100</v>
       </c>
       <c r="AA96" s="3">
         <v>-3800</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>-3800</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,235 +7267,247 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-9700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-7600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-25900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-9300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-29100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-7100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>8100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-11400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-13500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-16900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-27600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>32700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-10300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-22300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>30700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-28000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-11700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-4800</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-100</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
-      </c>
       <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
         <v>-200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E102" s="3">
         <v>18100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-16800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>12900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>14500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>16900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-31600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>22300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>11600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>8700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-12500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-9600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-17400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>18900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>59700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-7100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-2700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>7100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>13800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-29400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>13300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RGP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RGP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
   <si>
     <t>RGP</t>
   </si>
@@ -656,365 +656,378 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45528</v>
+      </c>
+      <c r="E7" s="2">
         <v>45437</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45346</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45255</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45164</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45073</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44982</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44891</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44800</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44709</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44618</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44528</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44436</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44345</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44254</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44163</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44072</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43981</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43883</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43792</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43701</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43610</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43519</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43428</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43337</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43246</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>136900</v>
+      </c>
+      <c r="E8" s="3">
         <v>148200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>151300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>163100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>170200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>184400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>186800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>200400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>204100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>217000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>204600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>200200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>183100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>172300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>156600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>153200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>147300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>178600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>168100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>184500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>172200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>182100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>179500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>188800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>178600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>183800</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>86900</v>
+      </c>
+      <c r="E9" s="3">
         <v>88600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>95300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>99700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>103200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>108700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>115200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>118000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>120600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>127400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>127800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>121500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>111700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>104000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>99600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>95000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>89400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>106400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>106600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>110100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>104700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>109200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>111600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>115400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>110400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>113400</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E10" s="3">
         <v>59600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>56000</v>
       </c>
-      <c r="F10" s="3">
-        <v>63400</v>
-      </c>
       <c r="G10" s="3">
+        <v>63500</v>
+      </c>
+      <c r="H10" s="3">
         <v>67000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>75700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>71600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>82400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>83500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>89600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>76800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>78700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>71400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>68300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>57000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>58200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>57900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>72200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>61500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>74400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>67500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>72900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>67900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>73400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>68200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>70400</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1043,8 +1056,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1123,8 +1137,11 @@
       <c r="AB12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1203,73 +1220,76 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-4200</v>
+        <v>5100</v>
       </c>
       <c r="E14" s="3">
-        <v>1600</v>
+        <v>-3500</v>
       </c>
       <c r="F14" s="3">
-        <v>2300</v>
+        <v>1800</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>700</v>
+        <v>3400</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I14" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J14" s="3">
         <v>2900</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>3400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>6600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-900</v>
-      </c>
-      <c r="V14" s="3">
-        <v>-100</v>
       </c>
       <c r="W14" s="3">
         <v>-100</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
+      <c r="X14" s="3">
+        <v>-100</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
@@ -1280,25 +1300,28 @@
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E15" s="3">
         <v>1900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2100</v>
-      </c>
-      <c r="G15" s="3">
-        <v>2200</v>
       </c>
       <c r="H15" s="3">
         <v>2200</v>
@@ -1307,64 +1330,67 @@
         <v>2200</v>
       </c>
       <c r="J15" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="K15" s="3">
         <v>2100</v>
       </c>
       <c r="L15" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="M15" s="3">
         <v>2200</v>
       </c>
       <c r="N15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="O15" s="3">
         <v>2100</v>
-      </c>
-      <c r="O15" s="3">
-        <v>2000</v>
       </c>
       <c r="P15" s="3">
         <v>2000</v>
       </c>
       <c r="Q15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="R15" s="3">
         <v>2200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>2400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2500</v>
-      </c>
-      <c r="T15" s="3">
-        <v>2700</v>
       </c>
       <c r="U15" s="3">
         <v>2700</v>
       </c>
       <c r="V15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="W15" s="3">
         <v>2900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2200</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>2100</v>
       </c>
       <c r="Z15" s="3">
         <v>2100</v>
       </c>
       <c r="AA15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AB15" s="3">
         <v>2000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1390,168 +1416,175 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>136900</v>
+        <v>136600</v>
       </c>
       <c r="E17" s="3">
-        <v>147000</v>
+        <v>140400</v>
       </c>
       <c r="F17" s="3">
-        <v>154800</v>
+        <v>145200</v>
       </c>
       <c r="G17" s="3">
+        <v>151400</v>
+      </c>
+      <c r="H17" s="3">
         <v>165300</v>
       </c>
-      <c r="H17" s="3">
-        <v>167400</v>
-      </c>
       <c r="I17" s="3">
-        <v>179700</v>
+        <v>167800</v>
       </c>
       <c r="J17" s="3">
+        <v>176700</v>
+      </c>
+      <c r="K17" s="3">
         <v>176900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>178900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>188900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>187100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>180500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>165100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>156900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>154600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>152000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>143100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>171100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>164600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>166800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>164200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>168300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>169300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>172500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>168800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>174300</v>
       </c>
     </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>11300</v>
+        <v>300</v>
       </c>
       <c r="E18" s="3">
-        <v>4300</v>
+        <v>7800</v>
       </c>
       <c r="F18" s="3">
-        <v>8300</v>
+        <v>6100</v>
       </c>
       <c r="G18" s="3">
+        <v>11700</v>
+      </c>
+      <c r="H18" s="3">
         <v>4900</v>
       </c>
-      <c r="H18" s="3">
-        <v>17000</v>
-      </c>
       <c r="I18" s="3">
-        <v>7100</v>
+        <v>16600</v>
       </c>
       <c r="J18" s="3">
+        <v>10100</v>
+      </c>
+      <c r="K18" s="3">
         <v>23500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>25200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>28100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>17500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>19700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>18000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>15400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>4200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>17700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>8000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>13800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>10200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>16300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>9800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1580,191 +1613,198 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="M20" s="3">
         <v>-300</v>
       </c>
       <c r="N20" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="O20" s="3">
         <v>100</v>
       </c>
       <c r="P20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-300</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>100</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-500</v>
       </c>
       <c r="U20" s="3">
         <v>-500</v>
       </c>
       <c r="V20" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
         <v>0</v>
       </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>13500</v>
+        <v>2300</v>
       </c>
       <c r="E21" s="3">
-        <v>6600</v>
+        <v>9700</v>
       </c>
       <c r="F21" s="3">
-        <v>10800</v>
+        <v>8200</v>
       </c>
       <c r="G21" s="3">
-        <v>7400</v>
+        <v>13900</v>
       </c>
       <c r="H21" s="3">
-        <v>19300</v>
+        <v>7100</v>
       </c>
       <c r="I21" s="3">
-        <v>9200</v>
+        <v>18900</v>
       </c>
       <c r="J21" s="3">
+        <v>12300</v>
+      </c>
+      <c r="K21" s="3">
         <v>25400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>27300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>29900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>19400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>21900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>20100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>17500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>3900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>6800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>9700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>20600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>10000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>16200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>12400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>18500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>11900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1787,8 +1827,8 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>8</v>
+      <c r="R22" s="3">
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>8</v>
@@ -1805,14 +1845,14 @@
       <c r="W22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y22" s="3">
         <v>600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>700</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>600</v>
       </c>
       <c r="AA22" s="3">
         <v>600</v>
@@ -1820,168 +1860,177 @@
       <c r="AB22" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E23" s="3">
         <v>11500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>8600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>17200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>23300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>25100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>27800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>17200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>19900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>18100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>15400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>4200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>7000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>3000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>17700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>7600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>13400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>9600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>15700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>9200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E24" s="3">
         <v>1000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5400</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>5900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-4000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>4000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>3500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2060,168 +2109,177 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E26" s="3">
         <v>10500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>11800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>17400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>18100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>20500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>19400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>14300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>12900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>23200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-1000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>6900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>12300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>9400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>5800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>10600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>5700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E27" s="3">
         <v>10500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>2600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>11800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>7000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>17400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>18100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>20500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>19400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>14300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>12900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>23200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>6900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>12300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>9400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>5800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>10600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>5700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2300,8 +2358,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2359,8 +2420,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2377,11 +2438,14 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2460,8 +2524,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2540,168 +2607,177 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="M32" s="3">
         <v>300</v>
       </c>
       <c r="N32" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="O32" s="3">
         <v>-100</v>
       </c>
       <c r="P32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>300</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
-      </c>
-      <c r="T32" s="3">
-        <v>500</v>
       </c>
       <c r="U32" s="3">
         <v>500</v>
       </c>
       <c r="V32" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
         <v>0</v>
       </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E33" s="3">
         <v>10500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>11800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>7000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>17400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>18100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>20500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>19400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>14300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>12900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>23200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-1000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>6900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>12300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>4900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>9400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>5800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>10600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>5700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2780,173 +2856,182 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E35" s="3">
         <v>10500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>11800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>7000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>17400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>18100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>20500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>19400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>14300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>12900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>23200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-1000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>6900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>12300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>4900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>9400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>5800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>10600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>5700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45528</v>
+      </c>
+      <c r="E38" s="2">
         <v>45437</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45346</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45255</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45164</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45073</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44982</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44891</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44800</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44709</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44618</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44528</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44436</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44345</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44254</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44163</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44072</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43981</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43883</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43792</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43701</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43610</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43519</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43428</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43337</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43246</v>
       </c>
     </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2975,8 +3060,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3005,88 +3091,92 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>89600</v>
+      </c>
+      <c r="E41" s="3">
         <v>108900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>113800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>95800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>112600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>116800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>103900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>89400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>72600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>104200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>82200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>70600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>61900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>74400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>84000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>97200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>114600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>95600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>35900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>43000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>45700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>43000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>48000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>40800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>27100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>56500</v>
       </c>
     </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3151,10 +3241,10 @@
         <v>0</v>
       </c>
       <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
         <v>6000</v>
-      </c>
-      <c r="Y42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z42" s="3" t="s">
         <v>8</v>
@@ -3165,111 +3255,117 @@
       <c r="AB42" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>114600</v>
+      </c>
+      <c r="E43" s="3">
         <v>116100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>120200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>138200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>135100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>142100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>151600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>182700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>183900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>188300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>187700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>182600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>164600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>153600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>119900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>114300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>111000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>129200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>138000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>138700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>130300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>135500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>142000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>147600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>138600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>131200</v>
       </c>
     </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -3325,191 +3421,200 @@
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>15800</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E45" s="3">
-        <v>17300</v>
+        <v>8900</v>
       </c>
       <c r="F45" s="3">
-        <v>8200</v>
-      </c>
-      <c r="G45" s="3">
-        <v>5800</v>
-      </c>
-      <c r="H45" s="3">
-        <v>5200</v>
-      </c>
-      <c r="I45" s="3">
-        <v>7000</v>
-      </c>
-      <c r="J45" s="3">
+        <v>8900</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>6600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>5700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>16000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7800</v>
-      </c>
-      <c r="N45" s="3">
-        <v>6700</v>
       </c>
       <c r="O45" s="3">
         <v>6700</v>
       </c>
       <c r="P45" s="3">
+        <v>6700</v>
+      </c>
+      <c r="Q45" s="3">
         <v>7200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>8100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>7100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>8000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>7700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>7400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>8100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>7000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>6800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>211500</v>
+      </c>
+      <c r="E46" s="3">
         <v>240800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>251300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>242200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>253500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>264100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>262600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>278700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>262200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>308500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>277800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>260000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>233300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>235300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>212000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>218600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>231500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>231000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>182000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>189400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>183400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>191700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>198000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>195400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>172500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>194900</v>
       </c>
     </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3565,168 +3670,177 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E48" s="3">
         <v>15700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>17500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>28600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>30000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>31200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>32600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>35200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>36500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>35200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>38100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>40500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>42700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>45200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>49000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>52300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>56200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>57900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>63000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>65100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>66100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>26600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>25700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>23700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>22600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>226200</v>
+        <v>243800</v>
       </c>
       <c r="E49" s="3">
-        <v>227900</v>
+        <v>242300</v>
       </c>
       <c r="F49" s="3">
-        <v>229500</v>
+        <v>242000</v>
       </c>
       <c r="G49" s="3">
-        <v>217200</v>
+        <v>241400</v>
       </c>
       <c r="H49" s="3">
-        <v>218200</v>
+        <v>226300</v>
       </c>
       <c r="I49" s="3">
-        <v>218800</v>
+        <v>224200</v>
       </c>
       <c r="J49" s="3">
+        <v>222000</v>
+      </c>
+      <c r="K49" s="3">
         <v>222800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>223100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>225500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>232800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>234200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>235600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>237000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>237100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>237300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>234800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>234100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>235100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>236400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>242200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>205400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>206700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>207700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>209400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>210500</v>
       </c>
     </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3805,8 +3919,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3885,88 +4002,94 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>28300</v>
+        <v>800</v>
       </c>
       <c r="E52" s="3">
-        <v>26500</v>
+        <v>900</v>
       </c>
       <c r="F52" s="3">
-        <v>24600</v>
+        <v>1400</v>
       </c>
       <c r="G52" s="3">
-        <v>21600</v>
+        <v>1600</v>
       </c>
       <c r="H52" s="3">
-        <v>18500</v>
+        <v>1600</v>
       </c>
       <c r="I52" s="3">
-        <v>18400</v>
+        <v>1800</v>
       </c>
       <c r="J52" s="3">
+        <v>4900</v>
+      </c>
+      <c r="K52" s="3">
         <v>13800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>11000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>4000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4045,88 +4168,94 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>512900</v>
+      </c>
+      <c r="E54" s="3">
         <v>510900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>523200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>524900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>522400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>532000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>532300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>550500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>534000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>581500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>559700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>538200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>514600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>520600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>501600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>512000</v>
-      </c>
-      <c r="S54" s="3">
-        <v>529200</v>
       </c>
       <c r="T54" s="3">
         <v>529200</v>
       </c>
       <c r="U54" s="3">
+        <v>529200</v>
+      </c>
+      <c r="V54" s="3">
         <v>486000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>496400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>496600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>428400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>435100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>431300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>408400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>432700</v>
       </c>
     </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4155,8 +4284,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4185,111 +4315,115 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E57" s="3">
         <v>15200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>17400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>17500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>15700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>16500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>16600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>13600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>17800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>15900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>18100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>16000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>17500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>20300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>15300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>15800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>18600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>20100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>22800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>21600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>22400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>22300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>22000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>23300</v>
       </c>
     </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>4700</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>6300</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>7500</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>7700</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -4345,236 +4479,245 @@
       <c r="AB58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>57200</v>
+        <v>10700</v>
       </c>
       <c r="E59" s="3">
-        <v>66800</v>
+        <v>10500</v>
       </c>
       <c r="F59" s="3">
-        <v>69200</v>
+        <v>12700</v>
       </c>
       <c r="G59" s="3">
-        <v>68200</v>
+        <v>13400</v>
       </c>
       <c r="H59" s="3">
-        <v>82600</v>
+        <v>10400</v>
       </c>
       <c r="I59" s="3">
-        <v>85500</v>
+        <v>10400</v>
       </c>
       <c r="J59" s="3">
+        <v>11100</v>
+      </c>
+      <c r="K59" s="3">
         <v>84400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>78900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>110700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>97900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>83200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>77200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>84900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>85900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>71300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>72800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>79100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>72200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>77900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>66300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>69800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>58900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>63300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>50600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>71200</v>
       </c>
     </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>74600</v>
+      </c>
+      <c r="E60" s="3">
         <v>72400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>84100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>86800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>83900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>97100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>102100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>101000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>91800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>124300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>115600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>99100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>95400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>100900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>103400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>91600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>88100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>94900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>90800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>97900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>89000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>91400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>81300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>85600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>72600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>94500</v>
       </c>
     </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>19300</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>8600</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>9300</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>10300</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>9800</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>10300</v>
       </c>
       <c r="J61" s="3">
-        <v>20000</v>
+        <v>11500</v>
       </c>
       <c r="K61" s="3">
         <v>20000</v>
       </c>
       <c r="L61" s="3">
-        <v>54000</v>
+        <v>20000</v>
       </c>
       <c r="M61" s="3">
         <v>54000</v>
       </c>
       <c r="N61" s="3">
+        <v>54000</v>
+      </c>
+      <c r="O61" s="3">
         <v>44000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>33000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>43000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>53000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>68000</v>
-      </c>
-      <c r="S61" s="3">
-        <v>88000</v>
       </c>
       <c r="T61" s="3">
         <v>88000</v>
       </c>
       <c r="U61" s="3">
+        <v>88000</v>
+      </c>
+      <c r="V61" s="3">
         <v>49000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>54000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>73000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>43000</v>
-      </c>
-      <c r="Y61" s="3">
-        <v>58000</v>
       </c>
       <c r="Z61" s="3">
         <v>58000</v>
@@ -4583,90 +4726,96 @@
         <v>58000</v>
       </c>
       <c r="AB61" s="3">
+        <v>58000</v>
+      </c>
+      <c r="AC61" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>19700</v>
+        <v>2400</v>
       </c>
       <c r="E62" s="3">
-        <v>24200</v>
+        <v>2500</v>
       </c>
       <c r="F62" s="3">
-        <v>24500</v>
+        <v>5300</v>
       </c>
       <c r="G62" s="3">
-        <v>19700</v>
+        <v>5300</v>
       </c>
       <c r="H62" s="3">
-        <v>20400</v>
+        <v>3100</v>
       </c>
       <c r="I62" s="3">
-        <v>23400</v>
+        <v>3000</v>
       </c>
       <c r="J62" s="3">
+        <v>3200</v>
+      </c>
+      <c r="K62" s="3">
         <v>27400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>30300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>30700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>33100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>41500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>45400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>47200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>37600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>45400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>43200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>42600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>43400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>44200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>46200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>11600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>12500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>10300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>9500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4745,8 +4894,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4825,8 +4977,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4905,88 +5060,94 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>105700</v>
+      </c>
+      <c r="E66" s="3">
         <v>92200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>108300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>111300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>103500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>117500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>125500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>148400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>142100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>209000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>202700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>184600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>173800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>191100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>194000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>205000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>219200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>225500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>183200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>196100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>208200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>146000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>151800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>153900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>140100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>163800</v>
       </c>
     </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5015,8 +5176,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5095,8 +5257,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5175,8 +5340,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5255,8 +5423,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5335,88 +5506,94 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E72" s="3">
         <v>88600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>83000</v>
-      </c>
-      <c r="F72" s="3">
-        <v>85900</v>
       </c>
       <c r="G72" s="3">
         <v>85900</v>
       </c>
       <c r="H72" s="3">
+        <v>85900</v>
+      </c>
+      <c r="I72" s="3">
         <v>87600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>80700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>78600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>66100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>52700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>36900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>22200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>375400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>367200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>348700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>352700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>358300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>360500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>361000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>358500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>350700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>350200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>345000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>343800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>337400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>335700</v>
       </c>
     </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5495,8 +5672,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5575,8 +5755,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5655,88 +5838,94 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>407200</v>
+      </c>
+      <c r="E76" s="3">
         <v>418800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>414900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>413600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>418800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>414500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>406800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>402100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>392000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>372400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>357000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>353600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>340800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>329500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>307600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>306900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>309900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>303700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>302800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>300300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>288400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>282400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>283300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>277400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>268300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>268800</v>
       </c>
     </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5815,173 +6004,182 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45528</v>
+      </c>
+      <c r="E80" s="2">
         <v>45437</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45346</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45255</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45164</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45073</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44982</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44891</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44800</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44709</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44618</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44528</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44436</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44345</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44254</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44163</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44072</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43981</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43883</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43792</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43701</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43610</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43519</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43428</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43337</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43246</v>
       </c>
     </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E81" s="3">
         <v>10500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>11800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>7000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>17400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>18100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>20500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>19400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>14300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>12900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>23200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-1000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>6900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>12300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>4900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>9400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>5800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>10600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>5700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6010,88 +6208,92 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1900</v>
+        <v>900</v>
       </c>
       <c r="E83" s="3">
-        <v>2200</v>
+        <v>900</v>
       </c>
       <c r="F83" s="3">
-        <v>2100</v>
+        <v>900</v>
       </c>
       <c r="G83" s="3">
-        <v>2200</v>
+        <v>900</v>
       </c>
       <c r="H83" s="3">
-        <v>2200</v>
+        <v>900</v>
       </c>
       <c r="I83" s="3">
-        <v>2200</v>
+        <v>900</v>
       </c>
       <c r="J83" s="3">
-        <v>2100</v>
+        <v>900</v>
       </c>
       <c r="K83" s="3">
         <v>2100</v>
       </c>
       <c r="L83" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="M83" s="3">
         <v>2200</v>
       </c>
       <c r="N83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="O83" s="3">
         <v>2100</v>
-      </c>
-      <c r="O83" s="3">
-        <v>2000</v>
       </c>
       <c r="P83" s="3">
         <v>2000</v>
       </c>
       <c r="Q83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="R83" s="3">
         <v>2200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2500</v>
-      </c>
-      <c r="T83" s="3">
-        <v>2700</v>
       </c>
       <c r="U83" s="3">
         <v>2700</v>
       </c>
       <c r="V83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="W83" s="3">
         <v>2900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2200</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>2100</v>
       </c>
       <c r="Z83" s="3">
         <v>2100</v>
       </c>
       <c r="AA83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AB83" s="3">
         <v>2000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6170,8 +6372,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6250,8 +6455,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6330,8 +6538,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6410,8 +6621,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6490,88 +6704,94 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E89" s="3">
         <v>3200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>20500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>17800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>40200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>29000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>26800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>19200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>11000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>18600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>28000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>20300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-3000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>30100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>11800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>18300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-16600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6600,46 +6820,47 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>-300</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
       </c>
       <c r="F91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-700</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-300</v>
       </c>
       <c r="M91" s="3">
         <v>-300</v>
       </c>
       <c r="N91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O91" s="3">
         <v>-1300</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-1000</v>
       </c>
       <c r="P91" s="3">
         <v>-1000</v>
@@ -6648,40 +6869,43 @@
         <v>-1000</v>
       </c>
       <c r="R91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="S91" s="3">
         <v>-1500</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-300</v>
       </c>
       <c r="T91" s="3">
         <v>-300</v>
       </c>
       <c r="U91" s="3">
-        <v>-800</v>
+        <v>-300</v>
       </c>
       <c r="V91" s="3">
         <v>-800</v>
       </c>
       <c r="W91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="X91" s="3">
         <v>-500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6760,8 +6984,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6840,88 +7067,94 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>2400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>2300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1300</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-1000</v>
       </c>
       <c r="P94" s="3">
         <v>-1000</v>
       </c>
       <c r="Q94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="R94" s="3">
         <v>-1200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-24800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6950,43 +7183,44 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E96" s="3">
+        <v>4700</v>
+      </c>
+      <c r="F96" s="3">
+        <v>4700</v>
+      </c>
+      <c r="G96" s="3">
+        <v>4700</v>
+      </c>
+      <c r="H96" s="3">
+        <v>4700</v>
+      </c>
+      <c r="I96" s="3">
+        <v>4700</v>
+      </c>
+      <c r="J96" s="3">
+        <v>4700</v>
+      </c>
+      <c r="K96" s="3">
         <v>-4700</v>
-      </c>
-      <c r="E96" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="F96" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="G96" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-4600</v>
       </c>
       <c r="L96" s="3">
         <v>-4600</v>
       </c>
       <c r="M96" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="N96" s="3">
         <v>-4700</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-4600</v>
       </c>
       <c r="O96" s="3">
         <v>-4600</v>
@@ -6998,7 +7232,7 @@
         <v>-4600</v>
       </c>
       <c r="R96" s="3">
-        <v>-4500</v>
+        <v>-4600</v>
       </c>
       <c r="S96" s="3">
         <v>-4500</v>
@@ -7013,7 +7247,7 @@
         <v>-4500</v>
       </c>
       <c r="W96" s="3">
-        <v>-4100</v>
+        <v>-4500</v>
       </c>
       <c r="X96" s="3">
         <v>-4100</v>
@@ -7025,13 +7259,16 @@
         <v>-4100</v>
       </c>
       <c r="AA96" s="3">
-        <v>-3800</v>
+        <v>-4100</v>
       </c>
       <c r="AB96" s="3">
         <v>-3800</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>-3800</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7110,8 +7347,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7190,8 +7430,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7270,8 +7513,11 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -7279,235 +7525,244 @@
         <v>-7700</v>
       </c>
       <c r="E100" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-9700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-7600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-25900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-9300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-29100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-7100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>8100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-11400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-13500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-16900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-27600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>32700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-10300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-22300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>30700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-28000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-11700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-4800</v>
       </c>
     </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-300</v>
+        <v>100</v>
       </c>
       <c r="E101" s="3">
+        <v>300</v>
+      </c>
+      <c r="F101" s="3">
+        <v>400</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="H101" s="3">
+        <v>500</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J101" s="3">
         <v>-400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="K101" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="L101" s="3">
+        <v>500</v>
+      </c>
+      <c r="M101" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="P101" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>300</v>
+      </c>
+      <c r="R101" s="3">
+        <v>-900</v>
+      </c>
+      <c r="S101" s="3">
+        <v>600</v>
+      </c>
+      <c r="T101" s="3">
+        <v>2100</v>
+      </c>
+      <c r="U101" s="3">
+        <v>-700</v>
+      </c>
+      <c r="V101" s="3">
         <v>-100</v>
       </c>
-      <c r="G101" s="3">
-        <v>100</v>
-      </c>
-      <c r="H101" s="3">
-        <v>300</v>
-      </c>
-      <c r="I101" s="3">
-        <v>400</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-2300</v>
-      </c>
-      <c r="K101" s="3">
-        <v>500</v>
-      </c>
-      <c r="L101" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-400</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="O101" s="3">
-        <v>-600</v>
-      </c>
-      <c r="P101" s="3">
-        <v>300</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>-900</v>
-      </c>
-      <c r="R101" s="3">
-        <v>600</v>
-      </c>
-      <c r="S101" s="3">
-        <v>2100</v>
-      </c>
-      <c r="T101" s="3">
-        <v>-700</v>
-      </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-100</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
-      <c r="W101" s="3">
-        <v>-200</v>
-      </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA101" s="3">
+        <v>-500</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-100</v>
       </c>
-      <c r="Y101" s="3">
-        <v>200</v>
-      </c>
-      <c r="Z101" s="3">
-        <v>-500</v>
-      </c>
-      <c r="AA101" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-19300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>18100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-16800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>12900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>14500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>16900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-31600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>22300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>11600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>8700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-12500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-9600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-13200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-17400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>18900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>59700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-7100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-4900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>7100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>13800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-29400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>13300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RGP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RGP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
   <si>
     <t>RGP</t>
   </si>
@@ -656,378 +656,390 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45619</v>
+      </c>
+      <c r="E7" s="2">
         <v>45528</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45437</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45346</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45255</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45164</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45073</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44982</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44891</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44800</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44709</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44618</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44528</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44436</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44345</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44254</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44163</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44072</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43981</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43883</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43792</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43701</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43610</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43519</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43428</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43337</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43246</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>145600</v>
+      </c>
+      <c r="E8" s="3">
         <v>136900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>148200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>151300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>163100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>170200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>184400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>186800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>200400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>204100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>217000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>204600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>200200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>183100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>172300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>156600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>153200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>147300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>178600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>168100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>184500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>172200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>182100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>179500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>188800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>178600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>183800</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>89500</v>
+      </c>
+      <c r="E9" s="3">
         <v>86900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>88600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>95300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>99700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>103200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>108700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>115200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>118000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>120600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>127400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>127800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>121500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>111700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>104000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>99600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>95000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>89400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>106400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>106600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>110100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>104700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>109200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>111600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>115400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>110400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>113400</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>56100</v>
+      </c>
+      <c r="E10" s="3">
         <v>50000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>59600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>56000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>63500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>67000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>75700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>71600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>82400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>83500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>89600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>76800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>78700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>71400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>68300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>57000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>58200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>57900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>72200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>61500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>74400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>67500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>72900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>67900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>73400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>68200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>70400</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1057,8 +1069,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1140,8 +1153,11 @@
       <c r="AC12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1223,76 +1239,79 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>80300</v>
+      </c>
+      <c r="E14" s="3">
         <v>5100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-3500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>3400</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2900</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>3400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>6600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-900</v>
-      </c>
-      <c r="W14" s="3">
-        <v>-100</v>
       </c>
       <c r="X14" s="3">
         <v>-100</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
+      <c r="Y14" s="3">
+        <v>-100</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
@@ -1303,11 +1322,14 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1315,16 +1337,16 @@
         <v>2000</v>
       </c>
       <c r="E15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F15" s="3">
         <v>1900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2100</v>
-      </c>
-      <c r="H15" s="3">
-        <v>2200</v>
       </c>
       <c r="I15" s="3">
         <v>2200</v>
@@ -1333,64 +1355,67 @@
         <v>2200</v>
       </c>
       <c r="K15" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="L15" s="3">
         <v>2100</v>
       </c>
       <c r="M15" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="N15" s="3">
         <v>2200</v>
       </c>
       <c r="O15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="P15" s="3">
         <v>2100</v>
-      </c>
-      <c r="P15" s="3">
-        <v>2000</v>
       </c>
       <c r="Q15" s="3">
         <v>2000</v>
       </c>
       <c r="R15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="S15" s="3">
         <v>2200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2500</v>
-      </c>
-      <c r="U15" s="3">
-        <v>2700</v>
       </c>
       <c r="V15" s="3">
         <v>2700</v>
       </c>
       <c r="W15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="X15" s="3">
         <v>2900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2200</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>2100</v>
       </c>
       <c r="AA15" s="3">
         <v>2100</v>
       </c>
       <c r="AB15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AC15" s="3">
         <v>2000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1417,174 +1442,181 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>142100</v>
+      </c>
+      <c r="E17" s="3">
         <v>136600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>140400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>145200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>151400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>165300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>167800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>176700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>176900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>178900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>188900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>187100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>180500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>165100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>156900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>154600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>152000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>143100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>171100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>164600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>166800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>164200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>168300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>169300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>172500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>168800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>174300</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E18" s="3">
         <v>300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>7800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>6100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>11700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>16600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>10100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>23500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>25200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>28100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>17500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>19700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>18000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>15400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>7500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>17700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>8000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>13800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>10200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>16300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>9800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1614,13 +1646,14 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1641,147 +1674,153 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3">
         <v>-300</v>
       </c>
       <c r="O20" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="P20" s="3">
         <v>100</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-300</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-500</v>
       </c>
       <c r="V20" s="3">
         <v>-500</v>
       </c>
       <c r="W20" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E21" s="3">
         <v>2300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>9700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>8200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>13900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>18900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>12300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>25400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>27300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>29900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>19400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>21900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>20100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>17500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>3900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>6800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>9700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>20600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>10000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>16200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>12400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>18500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>11900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1800,15 +1839,15 @@
       <c r="H22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I22" s="3">
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3">
         <v>-100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -1830,8 +1869,8 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>8</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>8</v>
@@ -1848,14 +1887,14 @@
       <c r="X22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z22" s="3">
         <v>600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>700</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>600</v>
       </c>
       <c r="AB22" s="3">
         <v>600</v>
@@ -1863,174 +1902,183 @@
       <c r="AC22" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-76400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-4700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>11500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>8600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>17200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>23300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>25100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>27800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>17200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>19900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>18100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>15400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>7000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>3000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>17700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>7600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>13400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>9600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>15700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>9200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E24" s="3">
         <v>1100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5400</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>5900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-2200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-7800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-4000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>3800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>3500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2112,174 +2160,183 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-68700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-5700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>10500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>4900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>11800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>17400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>18100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>20500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>19400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>14300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>12900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>23200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>6900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>12300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>9400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>5800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>10600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>5700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-68700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>10500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>11800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>17400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>18100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>20500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>19400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>14300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>12900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>23200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>6900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>12300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>9400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>5800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>10600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>5700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2361,8 +2418,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2423,8 +2483,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2441,11 +2501,14 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2527,8 +2590,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2610,13 +2676,16 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -2637,147 +2706,153 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="N32" s="3">
         <v>300</v>
       </c>
       <c r="O32" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="P32" s="3">
         <v>-100</v>
       </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>300</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
-      </c>
-      <c r="U32" s="3">
-        <v>500</v>
       </c>
       <c r="V32" s="3">
         <v>500</v>
       </c>
       <c r="W32" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-68700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>10500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>11800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>17400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>18100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>20500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>19400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>14300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>12900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>23200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>6900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>12300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>9400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>5800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>10600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>5700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2859,179 +2934,188 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-68700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>10500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>11800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>17400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>18100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>20500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>19400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>14300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>12900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>23200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>6900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>12300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>9400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>5800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>10600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>5700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45619</v>
+      </c>
+      <c r="E38" s="2">
         <v>45528</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45437</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45346</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45255</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45164</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45073</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44982</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44891</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44800</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44709</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44618</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44528</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44436</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44345</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44254</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44163</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44072</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43981</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43883</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43792</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43701</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43610</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43519</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43428</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43337</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43246</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3061,8 +3145,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3092,91 +3177,95 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>78200</v>
+      </c>
+      <c r="E41" s="3">
         <v>89600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>108900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>113800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>95800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>112600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>116800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>103900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>89400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>72600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>104200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>82200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>70600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>61900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>74400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>84000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>97200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>114600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>95600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>35900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>43000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>45700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>43000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>48000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>40800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>27100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>56500</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3244,10 +3333,10 @@
         <v>0</v>
       </c>
       <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="3">
         <v>6000</v>
-      </c>
-      <c r="Z42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA42" s="3" t="s">
         <v>8</v>
@@ -3258,91 +3347,97 @@
       <c r="AC42" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>115000</v>
+      </c>
+      <c r="E43" s="3">
         <v>114600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>116100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>120200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>138200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>135100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>142100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>151600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>182700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>183900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>188300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>187700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>182600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>164600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>153600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>119900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>114300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>111000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>129200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>138000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>138700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>130300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>135500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>142000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>147600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>138600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>131200</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3367,8 +3462,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -3424,22 +3519,25 @@
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3">
-        <v>8900</v>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F45" s="3">
         <v>8900</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
+      <c r="G45" s="3">
+        <v>8900</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>8</v>
@@ -3450,148 +3548,154 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>6600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>16000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7800</v>
-      </c>
-      <c r="O45" s="3">
-        <v>6700</v>
       </c>
       <c r="P45" s="3">
         <v>6700</v>
       </c>
       <c r="Q45" s="3">
+        <v>6700</v>
+      </c>
+      <c r="R45" s="3">
         <v>7200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>8100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>8000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>7700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>8100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>7000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>6800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>201700</v>
+      </c>
+      <c r="E46" s="3">
         <v>211500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>240800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>251300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>242200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>253500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>264100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>262600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>278700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>262200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>308500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>277800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>260000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>233300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>235300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>212000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>218600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>231500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>231000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>182000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>189400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>183400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>191700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>198000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>195400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>172500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>194900</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3616,8 +3720,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3673,174 +3777,183 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>29500</v>
+      </c>
+      <c r="E48" s="3">
         <v>26900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>15700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>17500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>28600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>30000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>31200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>32600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>35200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>36500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>35200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>38100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>40500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>42700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>45200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>49000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>52300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>56200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>57900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>63000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>65100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>66100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>26600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>25700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>23700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>22600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>182000</v>
+      </c>
+      <c r="E49" s="3">
         <v>243800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>242300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>242000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>241400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>226300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>224200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>222000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>222800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>223100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>225500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>232800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>234200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>235600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>237000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>237100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>237300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>234800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>234100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>235100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>236400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>242200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>205400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>206700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>207700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>209400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>210500</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3922,8 +4035,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4005,91 +4121,97 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>600</v>
+      </c>
+      <c r="E52" s="3">
         <v>800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1400</v>
-      </c>
-      <c r="G52" s="3">
-        <v>1600</v>
       </c>
       <c r="H52" s="3">
         <v>1600</v>
       </c>
       <c r="I52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J52" s="3">
         <v>1800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>13800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>11000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>4500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>4000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4171,91 +4293,97 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>424900</v>
+      </c>
+      <c r="E54" s="3">
         <v>512900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>510900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>523200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>524900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>522400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>532000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>532300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>550500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>534000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>581500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>559700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>538200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>514600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>520600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>501600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>512000</v>
-      </c>
-      <c r="T54" s="3">
-        <v>529200</v>
       </c>
       <c r="U54" s="3">
         <v>529200</v>
       </c>
       <c r="V54" s="3">
+        <v>529200</v>
+      </c>
+      <c r="W54" s="3">
         <v>486000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>496400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>496600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>428400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>435100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>431300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>408400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>432700</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4285,8 +4413,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4316,118 +4445,122 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E57" s="3">
         <v>14000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>17400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>17500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>15700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>16500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>16600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>12900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>17800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>15900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>18100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>16000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>17500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>20300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>15300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>15800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>18600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>20100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>22800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>21600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>22400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>22300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>22000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>23300</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E58" s="3">
         <v>5500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>7500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7700</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -4482,245 +4615,254 @@
       <c r="AC58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E59" s="3">
         <v>10700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>13400</v>
-      </c>
-      <c r="H59" s="3">
-        <v>10400</v>
       </c>
       <c r="I59" s="3">
         <v>10400</v>
       </c>
       <c r="J59" s="3">
+        <v>10400</v>
+      </c>
+      <c r="K59" s="3">
         <v>11100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>84400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>78900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>110700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>97900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>83200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>77200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>84900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>85900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>71300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>72800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>79100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>72200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>77900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>66300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>69800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>58900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>63300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>50600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>71200</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>73600</v>
+      </c>
+      <c r="E60" s="3">
         <v>74600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>72400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>84100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>86800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>83900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>97100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>102100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>101000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>91800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>124300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>115600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>99100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>95400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>100900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>103400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>91600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>88100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>94900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>90800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>97900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>89000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>91400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>81300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>85600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>72600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>94500</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E61" s="3">
         <v>19300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>10300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>10300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>11500</v>
-      </c>
-      <c r="K61" s="3">
-        <v>20000</v>
       </c>
       <c r="L61" s="3">
         <v>20000</v>
       </c>
       <c r="M61" s="3">
-        <v>54000</v>
+        <v>20000</v>
       </c>
       <c r="N61" s="3">
         <v>54000</v>
       </c>
       <c r="O61" s="3">
+        <v>54000</v>
+      </c>
+      <c r="P61" s="3">
         <v>44000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>33000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>43000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>53000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>68000</v>
-      </c>
-      <c r="T61" s="3">
-        <v>88000</v>
       </c>
       <c r="U61" s="3">
         <v>88000</v>
       </c>
       <c r="V61" s="3">
+        <v>88000</v>
+      </c>
+      <c r="W61" s="3">
         <v>49000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>54000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>73000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>43000</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>58000</v>
       </c>
       <c r="AA61" s="3">
         <v>58000</v>
@@ -4729,93 +4871,99 @@
         <v>58000</v>
       </c>
       <c r="AC61" s="3">
+        <v>58000</v>
+      </c>
+      <c r="AD61" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E62" s="3">
         <v>2400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2500</v>
-      </c>
-      <c r="F62" s="3">
-        <v>5300</v>
       </c>
       <c r="G62" s="3">
         <v>5300</v>
       </c>
       <c r="H62" s="3">
+        <v>5300</v>
+      </c>
+      <c r="I62" s="3">
         <v>3100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>27400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>30300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>30700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>33100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>41500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>45400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>47200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>37600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>45400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>43200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>42600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>43400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>44200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>46200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>11600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>12500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>10300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>9500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4897,8 +5045,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4980,8 +5131,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5063,91 +5217,97 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>99200</v>
+      </c>
+      <c r="E66" s="3">
         <v>105700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>92200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>108300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>111300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>103500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>117500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>125500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>148400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>142100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>209000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>202700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>184600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>173800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>191100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>194000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>205000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>219200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>225500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>183200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>196100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>208200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>146000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>151800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>153900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>140100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>163800</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5177,8 +5337,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5260,8 +5421,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5343,8 +5507,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5426,8 +5593,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5509,91 +5679,97 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E72" s="3">
         <v>78000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>88600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>83000</v>
-      </c>
-      <c r="G72" s="3">
-        <v>85900</v>
       </c>
       <c r="H72" s="3">
         <v>85900</v>
       </c>
       <c r="I72" s="3">
+        <v>85900</v>
+      </c>
+      <c r="J72" s="3">
         <v>87600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>80700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>78600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>66100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>52700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>36900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>22200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>375400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>367200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>348700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>352700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>358300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>360500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>361000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>358500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>350700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>350200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>345000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>343800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>337400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>335700</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5675,8 +5851,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5758,8 +5937,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5841,91 +6023,97 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>325700</v>
+      </c>
+      <c r="E76" s="3">
         <v>407200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>418800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>414900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>413600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>418800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>414500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>406800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>402100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>392000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>372400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>357000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>353600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>340800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>329500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>307600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>306900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>309900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>303700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>302800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>300300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>288400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>282400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>283300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>277400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>268300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>268800</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6007,179 +6195,188 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45619</v>
+      </c>
+      <c r="E80" s="2">
         <v>45528</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45437</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45346</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45255</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45164</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45073</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44982</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44891</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44800</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44709</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44618</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44528</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44436</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44345</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44254</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44163</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44072</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43981</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43883</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43792</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43701</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43610</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43519</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43428</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43337</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43246</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-68700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>10500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>11800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>17400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>18100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>20500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>19400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>14300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>12900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>23200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>6900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>12300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>9400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>5800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>10600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>5700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6209,13 +6406,14 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="E83" s="3">
         <v>900</v>
@@ -6236,64 +6434,67 @@
         <v>900</v>
       </c>
       <c r="K83" s="3">
-        <v>2100</v>
+        <v>900</v>
       </c>
       <c r="L83" s="3">
         <v>2100</v>
       </c>
       <c r="M83" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="N83" s="3">
         <v>2200</v>
       </c>
       <c r="O83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="P83" s="3">
         <v>2100</v>
-      </c>
-      <c r="P83" s="3">
-        <v>2000</v>
       </c>
       <c r="Q83" s="3">
         <v>2000</v>
       </c>
       <c r="R83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="S83" s="3">
         <v>2200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>2400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2500</v>
-      </c>
-      <c r="U83" s="3">
-        <v>2700</v>
       </c>
       <c r="V83" s="3">
         <v>2700</v>
       </c>
       <c r="W83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="X83" s="3">
         <v>2900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2200</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>2100</v>
       </c>
       <c r="AA83" s="3">
         <v>2100</v>
       </c>
       <c r="AB83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AC83" s="3">
         <v>2000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6375,8 +6576,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6458,8 +6662,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6541,8 +6748,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6624,8 +6834,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6707,91 +6920,97 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>20500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>17800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>40200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>29000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>26800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>19200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>5800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>11000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>18600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>28000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>20300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>30100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>11800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>18300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-16600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6821,49 +7040,50 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-100</v>
       </c>
       <c r="F91" s="3">
         <v>-100</v>
       </c>
       <c r="G91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-700</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-300</v>
       </c>
       <c r="N91" s="3">
         <v>-300</v>
       </c>
       <c r="O91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P91" s="3">
         <v>-1300</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-1000</v>
       </c>
       <c r="Q91" s="3">
         <v>-1000</v>
@@ -6872,40 +7092,43 @@
         <v>-1000</v>
       </c>
       <c r="S91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="T91" s="3">
         <v>-1500</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-300</v>
       </c>
       <c r="U91" s="3">
         <v>-300</v>
       </c>
       <c r="V91" s="3">
-        <v>-800</v>
+        <v>-300</v>
       </c>
       <c r="W91" s="3">
         <v>-800</v>
       </c>
       <c r="X91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6987,8 +7210,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7070,91 +7296,97 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>2400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>2300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1300</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-1000</v>
       </c>
       <c r="Q94" s="3">
         <v>-1000</v>
       </c>
       <c r="R94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="S94" s="3">
         <v>-1200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-24800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-6900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7184,8 +7416,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7211,19 +7444,19 @@
         <v>4700</v>
       </c>
       <c r="K96" s="3">
+        <v>4700</v>
+      </c>
+      <c r="L96" s="3">
         <v>-4700</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-4600</v>
       </c>
       <c r="M96" s="3">
         <v>-4600</v>
       </c>
       <c r="N96" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="O96" s="3">
         <v>-4700</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-4600</v>
       </c>
       <c r="P96" s="3">
         <v>-4600</v>
@@ -7235,7 +7468,7 @@
         <v>-4600</v>
       </c>
       <c r="S96" s="3">
-        <v>-4500</v>
+        <v>-4600</v>
       </c>
       <c r="T96" s="3">
         <v>-4500</v>
@@ -7250,7 +7483,7 @@
         <v>-4500</v>
       </c>
       <c r="X96" s="3">
-        <v>-4100</v>
+        <v>-4500</v>
       </c>
       <c r="Y96" s="3">
         <v>-4100</v>
@@ -7262,13 +7495,16 @@
         <v>-4100</v>
       </c>
       <c r="AB96" s="3">
-        <v>-3800</v>
+        <v>-4100</v>
       </c>
       <c r="AC96" s="3">
         <v>-3800</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>-3800</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7350,8 +7586,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7433,8 +7672,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7516,253 +7758,265 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-7700</v>
+        <v>-9700</v>
       </c>
       <c r="E100" s="3">
         <v>-7700</v>
       </c>
       <c r="F100" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="G100" s="3">
         <v>-1700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-9700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-7600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-25900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-9300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-29100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-7100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>8100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-11400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-13500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-16900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-27600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>32700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-10300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-22300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>30700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-28000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-11700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-4800</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
-      </c>
       <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-19300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>18100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-16800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>12900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>14500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>16900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-31600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>22300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>11600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>8700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-12500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-9600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-13200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-17400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>18900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>59700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-7100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>7100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>13800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-29400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>13300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RGP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RGP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
   <si>
     <t>RGP</t>
   </si>
@@ -656,390 +656,403 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45710</v>
+      </c>
+      <c r="E7" s="2">
         <v>45619</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45528</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45437</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45346</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45255</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45164</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45073</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44982</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44891</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44800</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44709</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44618</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44528</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44436</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44345</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44254</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44163</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44072</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43981</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43883</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43792</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43701</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43610</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43519</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43428</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43337</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43246</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>129400</v>
+      </c>
+      <c r="E8" s="3">
         <v>145600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>136900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>148200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>151300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>163100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>170200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>184400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>186800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>200400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>204100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>217000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>204600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>200200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>183100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>172300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>156600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>153200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>147300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>178600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>168100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>184500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>172200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>182100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>179500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>188800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>178600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>183800</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>84100</v>
+      </c>
+      <c r="E9" s="3">
         <v>89500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>86900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>88600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>95300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>99700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>103200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>108700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>115200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>118000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>120600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>127400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>127800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>121500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>111700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>104000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>99600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>95000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>89400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>106400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>106600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>110100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>104700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>109200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>111600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>115400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>110400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>113400</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E10" s="3">
         <v>56100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>50000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>59600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>56000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>63500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>67000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>75700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>71600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>82400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>83500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>89600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>76800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>78700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>71400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>68300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>57000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>58200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>57900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>72200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>61500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>74400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>67500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>72900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>67900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>73400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>68200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>70400</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1070,8 +1083,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1156,8 +1170,11 @@
       <c r="AD12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1242,79 +1259,82 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E14" s="3">
         <v>80300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>5100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-3500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3400</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2900</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>3400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>6600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-900</v>
-      </c>
-      <c r="X14" s="3">
-        <v>-100</v>
       </c>
       <c r="Y14" s="3">
         <v>-100</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
+      <c r="Z14" s="3">
+        <v>-100</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
@@ -1325,31 +1345,34 @@
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="E15" s="3">
         <v>2000</v>
       </c>
       <c r="F15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G15" s="3">
         <v>1900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2100</v>
-      </c>
-      <c r="I15" s="3">
-        <v>2200</v>
       </c>
       <c r="J15" s="3">
         <v>2200</v>
@@ -1358,64 +1381,67 @@
         <v>2200</v>
       </c>
       <c r="L15" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="M15" s="3">
         <v>2100</v>
       </c>
       <c r="N15" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="O15" s="3">
         <v>2200</v>
       </c>
       <c r="P15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Q15" s="3">
         <v>2100</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>2000</v>
       </c>
       <c r="R15" s="3">
         <v>2000</v>
       </c>
       <c r="S15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="T15" s="3">
         <v>2200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>2400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2500</v>
-      </c>
-      <c r="V15" s="3">
-        <v>2700</v>
       </c>
       <c r="W15" s="3">
         <v>2700</v>
       </c>
       <c r="X15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="Y15" s="3">
         <v>2900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>2200</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>2100</v>
       </c>
       <c r="AB15" s="3">
         <v>2100</v>
       </c>
       <c r="AC15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AD15" s="3">
         <v>2000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1443,180 +1469,187 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>133700</v>
+      </c>
+      <c r="E17" s="3">
         <v>142100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>136600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>140400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>145200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>151400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>165300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>167800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>176700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>176900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>178900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>188900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>187100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>180500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>165100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>156900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>154600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>152000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>143100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>171100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>164600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>166800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>164200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>168300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>169300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>172500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>168800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>174300</v>
       </c>
     </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E18" s="3">
         <v>3600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>6100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>11700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>16600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>10100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>23500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>25200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>28100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>17500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>19700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>18000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>15400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>7500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>17700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>8000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>13800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>10200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>16300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>9800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1647,17 +1680,18 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>-100</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
         <v>0</v>
       </c>
@@ -1677,150 +1711,156 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="O20" s="3">
         <v>-300</v>
       </c>
       <c r="P20" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="Q20" s="3">
         <v>100</v>
       </c>
       <c r="R20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-300</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>100</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-500</v>
       </c>
       <c r="W20" s="3">
         <v>-500</v>
       </c>
       <c r="X20" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E21" s="3">
         <v>5700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>9700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>13900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>18900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>12300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>25400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>27300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>29900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>19400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>21900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>20100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>17500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>3900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>6800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>9700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>5600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>20600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>10000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>16200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>12400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>18500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>11900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1842,15 +1882,15 @@
       <c r="I22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="3">
         <v>-100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -1872,8 +1912,8 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>8</v>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>8</v>
@@ -1890,14 +1930,14 @@
       <c r="Y22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="Z22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA22" s="3">
         <v>600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>700</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>600</v>
       </c>
       <c r="AC22" s="3">
         <v>600</v>
@@ -1905,180 +1945,189 @@
       <c r="AD22" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-49600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-76400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-4700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>11500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>8600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>17200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>23300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>25100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>27800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>17200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>19900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>18100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>15400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>7000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>3000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>17700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>7600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>13400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>9600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>15700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>9200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-5600</v>
+      </c>
+      <c r="E24" s="3">
         <v>-7700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5400</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>5900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>7000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-7800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-4000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>4000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>3800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>5100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2163,180 +2212,189 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-44100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-68700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-5700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>10500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>11800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>17400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>18100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>20500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>19400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>14300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>12900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>23200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-1000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>2300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>6900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>12300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>9400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>5800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>10600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>5700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-44100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-68700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>10500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>11800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>7000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>17400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>18100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>20500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>19400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>14300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>12900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>23200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>2300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>6900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>12300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>9400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>5800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>10600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>5700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2421,8 +2479,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2486,8 +2547,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2504,11 +2565,14 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2593,8 +2657,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2679,17 +2746,20 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>100</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
         <v>0</v>
       </c>
@@ -2709,150 +2779,156 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="O32" s="3">
         <v>300</v>
       </c>
       <c r="P32" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="Q32" s="3">
         <v>-100</v>
       </c>
       <c r="R32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>300</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
-      </c>
-      <c r="V32" s="3">
-        <v>500</v>
       </c>
       <c r="W32" s="3">
         <v>500</v>
       </c>
       <c r="X32" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-44100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-68700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>10500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>11800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>7000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>17400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>18100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>20500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>19400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>14300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>12900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>23200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-1000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>2300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>6900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>12300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>9400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>5800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>10600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>5700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2937,185 +3013,194 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-44100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-68700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>10500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>11800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>7000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>17400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>18100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>20500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>19400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>14300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>12900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>23200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-1000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>2300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>6900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>12300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>9400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>5800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>10600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>5700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45710</v>
+      </c>
+      <c r="E38" s="2">
         <v>45619</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45528</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45437</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45346</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45255</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45164</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45073</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44982</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44891</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44800</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44709</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44618</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44528</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44436</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44345</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44254</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44163</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44072</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43981</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43883</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43792</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43701</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43610</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43519</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43428</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43337</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43246</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3146,8 +3231,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3178,94 +3264,98 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>72500</v>
+      </c>
+      <c r="E41" s="3">
         <v>78200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>89600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>108900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>113800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>95800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>112600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>116800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>103900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>89400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>72600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>104200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>82200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>70600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>61900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>74400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>84000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>97200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>114600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>95600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>35900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>43000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>45700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>43000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>48000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>40800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>27100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>56500</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3336,10 +3426,10 @@
         <v>0</v>
       </c>
       <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3">
         <v>6000</v>
-      </c>
-      <c r="AA42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB42" s="3" t="s">
         <v>8</v>
@@ -3350,94 +3440,100 @@
       <c r="AD42" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>109800</v>
+      </c>
+      <c r="E43" s="3">
         <v>115000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>114600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>116100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>120200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>138200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>135100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>142100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>151600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>182700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>183900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>188300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>187700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>182600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>164600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>153600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>119900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>114300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>111000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>129200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>138000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>138700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>130300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>135500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>142000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>147600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>138600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>131200</v>
       </c>
     </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3465,8 +3561,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -3522,8 +3618,11 @@
       <c r="AD44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3533,14 +3632,14 @@
       <c r="E45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="3">
-        <v>8900</v>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G45" s="3">
         <v>8900</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
+      <c r="H45" s="3">
+        <v>8900</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>8</v>
@@ -3551,151 +3650,157 @@
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>6600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>16000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7800</v>
-      </c>
-      <c r="P45" s="3">
-        <v>6700</v>
       </c>
       <c r="Q45" s="3">
         <v>6700</v>
       </c>
       <c r="R45" s="3">
+        <v>6700</v>
+      </c>
+      <c r="S45" s="3">
         <v>7200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>8100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>6200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>8000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>7100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>8100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>7000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>6800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>195200</v>
+      </c>
+      <c r="E46" s="3">
         <v>201700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>211500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>240800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>251300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>242200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>253500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>264100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>262600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>278700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>262200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>308500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>277800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>260000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>233300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>235300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>212000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>218600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>231500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>231000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>182000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>189400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>183400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>191700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>198000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>195400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>172500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>194900</v>
       </c>
     </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3723,8 +3828,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3780,180 +3885,189 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>28000</v>
+      </c>
+      <c r="E48" s="3">
         <v>29500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>26900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>15700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>17500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>28600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>30000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>31200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>32600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>35200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>36500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>35200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>38100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>40500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>42700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>45200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>49000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>52300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>56200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>57900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>63000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>65100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>66100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>26600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>25700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>23700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>22600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>118400</v>
+      </c>
+      <c r="E49" s="3">
         <v>182000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>243800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>242300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>242000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>241400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>226300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>224200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>222000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>222800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>223100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>225500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>232800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>234200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>235600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>237000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>237100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>237300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>234800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>234100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>235100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>236400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>242200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>205400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>206700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>207700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>209400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>210500</v>
       </c>
     </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4038,8 +4152,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4124,94 +4241,100 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E52" s="3">
         <v>600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1400</v>
-      </c>
-      <c r="H52" s="3">
-        <v>1600</v>
       </c>
       <c r="I52" s="3">
         <v>1600</v>
       </c>
       <c r="J52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K52" s="3">
         <v>1800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>13800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>12200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>4600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>4500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>4000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4296,94 +4419,100 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>375600</v>
+      </c>
+      <c r="E54" s="3">
         <v>424900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>512900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>510900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>523200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>524900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>522400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>532000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>532300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>550500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>534000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>581500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>559700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>538200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>514600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>520600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>501600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>512000</v>
-      </c>
-      <c r="U54" s="3">
-        <v>529200</v>
       </c>
       <c r="V54" s="3">
         <v>529200</v>
       </c>
       <c r="W54" s="3">
+        <v>529200</v>
+      </c>
+      <c r="X54" s="3">
         <v>486000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>496400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>496600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>428400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>435100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>431300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>408400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>432700</v>
       </c>
     </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4414,8 +4543,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4446,124 +4576,128 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E57" s="3">
         <v>13600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>14000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>17400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>17500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>15700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>14500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>16500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>16600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>12900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>13600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>17800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>15900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>18100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>16000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>17500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>20300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>15300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>15800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>18600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>20100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>22800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>21600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>22400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>22300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>22000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>23300</v>
       </c>
     </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E58" s="3">
         <v>5400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>7500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7700</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -4618,254 +4752,263 @@
       <c r="AD58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E59" s="3">
         <v>9500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>10700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13400</v>
-      </c>
-      <c r="I59" s="3">
-        <v>10400</v>
       </c>
       <c r="J59" s="3">
         <v>10400</v>
       </c>
       <c r="K59" s="3">
+        <v>10400</v>
+      </c>
+      <c r="L59" s="3">
         <v>11100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>84400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>78900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>110700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>97900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>83200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>77200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>84900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>85900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>71300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>72800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>79100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>72200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>77900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>66300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>69800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>58900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>63300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>50600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>71200</v>
       </c>
     </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>74200</v>
+      </c>
+      <c r="E60" s="3">
         <v>73600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>74600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>72400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>84100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>86800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>83900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>97100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>102100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>101000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>91800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>124300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>115600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>99100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>95400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>100900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>103400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>91600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>88100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>94900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>90800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>97900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>89000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>91400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>81300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>85600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>72600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>94500</v>
       </c>
     </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>21300</v>
+      </c>
+      <c r="E61" s="3">
         <v>22400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>19300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>10300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>10300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>11500</v>
-      </c>
-      <c r="L61" s="3">
-        <v>20000</v>
       </c>
       <c r="M61" s="3">
         <v>20000</v>
       </c>
       <c r="N61" s="3">
-        <v>54000</v>
+        <v>20000</v>
       </c>
       <c r="O61" s="3">
         <v>54000</v>
       </c>
       <c r="P61" s="3">
+        <v>54000</v>
+      </c>
+      <c r="Q61" s="3">
         <v>44000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>33000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>43000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>53000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>68000</v>
-      </c>
-      <c r="U61" s="3">
-        <v>88000</v>
       </c>
       <c r="V61" s="3">
         <v>88000</v>
       </c>
       <c r="W61" s="3">
+        <v>88000</v>
+      </c>
+      <c r="X61" s="3">
         <v>49000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>54000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>73000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>43000</v>
-      </c>
-      <c r="AA61" s="3">
-        <v>58000</v>
       </c>
       <c r="AB61" s="3">
         <v>58000</v>
@@ -4874,96 +5017,102 @@
         <v>58000</v>
       </c>
       <c r="AD61" s="3">
+        <v>58000</v>
+      </c>
+      <c r="AE61" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E62" s="3">
         <v>2300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2500</v>
-      </c>
-      <c r="G62" s="3">
-        <v>5300</v>
       </c>
       <c r="H62" s="3">
         <v>5300</v>
       </c>
       <c r="I62" s="3">
+        <v>5300</v>
+      </c>
+      <c r="J62" s="3">
         <v>3100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>27400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>30300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>30700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>33100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>41500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>45400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>47200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>37600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>45400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>43200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>42600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>43400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>44200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>46200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>11600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>12500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>10300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>9500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5048,8 +5197,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5134,8 +5286,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5220,94 +5375,100 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>97800</v>
+      </c>
+      <c r="E66" s="3">
         <v>99200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>105700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>92200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>108300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>111300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>103500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>117500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>125500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>148400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>142100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>209000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>202700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>184600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>173800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>191100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>194000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>205000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>219200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>225500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>183200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>196100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>208200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>146000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>151800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>153900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>140100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>163800</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5338,8 +5499,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5424,8 +5586,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5510,8 +5675,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5596,8 +5764,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5682,94 +5853,100 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-45900</v>
+      </c>
+      <c r="E72" s="3">
         <v>4100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>78000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>88600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>83000</v>
-      </c>
-      <c r="H72" s="3">
-        <v>85900</v>
       </c>
       <c r="I72" s="3">
         <v>85900</v>
       </c>
       <c r="J72" s="3">
+        <v>85900</v>
+      </c>
+      <c r="K72" s="3">
         <v>87600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>80700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>78600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>66100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>52700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>36900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>22200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>375400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>367200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>348700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>352700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>358300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>360500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>361000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>358500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>350700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>350200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>345000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>343800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>337400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>335700</v>
       </c>
     </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5854,8 +6031,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5940,8 +6120,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6026,94 +6209,100 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>277800</v>
+      </c>
+      <c r="E76" s="3">
         <v>325700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>407200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>418800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>414900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>413600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>418800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>414500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>406800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>402100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>392000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>372400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>357000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>353600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>340800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>329500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>307600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>306900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>309900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>303700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>302800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>300300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>288400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>282400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>283300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>277400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>268300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>268800</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6198,185 +6387,194 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45710</v>
+      </c>
+      <c r="E80" s="2">
         <v>45619</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45528</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45437</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45346</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45255</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45164</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45073</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44982</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44891</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44800</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44709</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44618</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44528</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44436</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44345</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44254</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44163</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44072</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43981</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43883</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43792</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43701</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43610</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43519</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43428</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43337</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43246</v>
       </c>
     </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-44100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-68700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>10500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>11800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>7000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>17400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>18100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>20500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>19400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>14300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>12900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>23200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-1000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>2300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>6900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>12300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>9400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>5800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>10600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>5700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6407,16 +6605,17 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>700</v>
+      </c>
+      <c r="E83" s="3">
         <v>800</v>
-      </c>
-      <c r="E83" s="3">
-        <v>900</v>
       </c>
       <c r="F83" s="3">
         <v>900</v>
@@ -6437,64 +6636,67 @@
         <v>900</v>
       </c>
       <c r="L83" s="3">
-        <v>2100</v>
+        <v>900</v>
       </c>
       <c r="M83" s="3">
         <v>2100</v>
       </c>
       <c r="N83" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="O83" s="3">
         <v>2200</v>
       </c>
       <c r="P83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Q83" s="3">
         <v>2100</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>2000</v>
       </c>
       <c r="R83" s="3">
         <v>2000</v>
       </c>
       <c r="S83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="T83" s="3">
         <v>2200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>2400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2500</v>
-      </c>
-      <c r="V83" s="3">
-        <v>2700</v>
       </c>
       <c r="W83" s="3">
         <v>2700</v>
       </c>
       <c r="X83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="Y83" s="3">
         <v>2900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>2200</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>2100</v>
       </c>
       <c r="AB83" s="3">
         <v>2100</v>
       </c>
       <c r="AC83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AD83" s="3">
         <v>2000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6579,8 +6781,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6665,8 +6870,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6751,8 +6959,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6837,8 +7048,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6923,94 +7137,100 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>700</v>
+      </c>
+      <c r="E89" s="3">
         <v>1800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>20500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>17800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>40200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>29000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>26800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>19200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>5800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>11000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>18600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>28000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>20300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>30100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>11800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>18300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-16600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7041,52 +7261,53 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-100</v>
       </c>
       <c r="G91" s="3">
         <v>-100</v>
       </c>
       <c r="H91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I91" s="3">
         <v>-300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-700</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-300</v>
       </c>
       <c r="O91" s="3">
         <v>-300</v>
       </c>
       <c r="P91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="Q91" s="3">
         <v>-1300</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-1000</v>
       </c>
       <c r="R91" s="3">
         <v>-1000</v>
@@ -7095,40 +7316,43 @@
         <v>-1000</v>
       </c>
       <c r="T91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="U91" s="3">
         <v>-1500</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-300</v>
       </c>
       <c r="V91" s="3">
         <v>-300</v>
       </c>
       <c r="W91" s="3">
-        <v>-800</v>
+        <v>-300</v>
       </c>
       <c r="X91" s="3">
         <v>-800</v>
       </c>
       <c r="Y91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7213,8 +7437,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7299,94 +7526,100 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-10900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>2400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>2300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1300</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-1000</v>
       </c>
       <c r="R94" s="3">
         <v>-1000</v>
       </c>
       <c r="S94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="T94" s="3">
         <v>-1200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-24800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-6900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7417,13 +7650,14 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>4700</v>
+        <v>4600</v>
       </c>
       <c r="E96" s="3">
         <v>4700</v>
@@ -7447,19 +7681,19 @@
         <v>4700</v>
       </c>
       <c r="L96" s="3">
+        <v>4700</v>
+      </c>
+      <c r="M96" s="3">
         <v>-4700</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-4600</v>
       </c>
       <c r="N96" s="3">
         <v>-4600</v>
       </c>
       <c r="O96" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="P96" s="3">
         <v>-4700</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-4600</v>
       </c>
       <c r="Q96" s="3">
         <v>-4600</v>
@@ -7471,7 +7705,7 @@
         <v>-4600</v>
       </c>
       <c r="T96" s="3">
-        <v>-4500</v>
+        <v>-4600</v>
       </c>
       <c r="U96" s="3">
         <v>-4500</v>
@@ -7486,7 +7720,7 @@
         <v>-4500</v>
       </c>
       <c r="Y96" s="3">
-        <v>-4100</v>
+        <v>-4500</v>
       </c>
       <c r="Z96" s="3">
         <v>-4100</v>
@@ -7498,13 +7732,16 @@
         <v>-4100</v>
       </c>
       <c r="AC96" s="3">
-        <v>-3800</v>
+        <v>-4100</v>
       </c>
       <c r="AD96" s="3">
         <v>-3800</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>-3800</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7589,8 +7826,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7675,8 +7915,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7761,262 +8004,274 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-9700</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-7700</v>
       </c>
       <c r="F100" s="3">
         <v>-7700</v>
       </c>
       <c r="G100" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="H100" s="3">
         <v>-1700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-9700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-7600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-25900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-9300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-29100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-7100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>8100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-11400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-13500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-16900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-27600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>32700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-10300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-22300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>30700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-28000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-11700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-4800</v>
       </c>
     </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>2100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-100</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
-      </c>
       <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z101" s="3">
         <v>-200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-11400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-19300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>18100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-16800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>12900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>14500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>16900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-31600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>22300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>11600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>8700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-12500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-9600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-13200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-17400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>18900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>59700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-7100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-4900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>7100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>13800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-29400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>13300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RGP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RGP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="92">
   <si>
     <t>RGP</t>
   </si>
@@ -656,403 +656,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45808</v>
+      </c>
+      <c r="E7" s="2">
         <v>45710</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45619</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45528</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45437</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45346</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45255</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45164</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45073</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44982</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44891</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44800</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44709</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44618</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44528</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44436</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44345</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44254</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44163</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44072</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43981</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43883</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43792</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43701</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43610</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43519</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43428</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43337</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43246</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>139300</v>
+      </c>
+      <c r="E8" s="3">
         <v>129400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>145600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>136900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>148200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>151300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>163100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>170200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>184400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>186800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>200400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>204100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>217000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>204600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>200200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>183100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>172300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>156600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>153200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>147300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>178600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>168100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>184500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>172200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>182100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>179500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>188800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>178600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>183800</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>83400</v>
+      </c>
+      <c r="E9" s="3">
         <v>84100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>89500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>86900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>88600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>95300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>99700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>103200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>108700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>115200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>118000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>120600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>127400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>127800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>121500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>111700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>104000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>99600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>95000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>89400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>106400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>106600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>110100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>104700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>109200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>111600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>115400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>110400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>113400</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>56000</v>
+      </c>
+      <c r="E10" s="3">
         <v>45400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>56100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>50000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>59600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>56000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>63500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>67000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>75700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>71600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>82400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>83500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>89600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>76800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>78700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>71400</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>68300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>57000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>58200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>57900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>72200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>61500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>74400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>67500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>72900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>67900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>73400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>68200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>70400</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1173,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,82 +1279,85 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>71400</v>
+      </c>
+      <c r="E14" s="3">
         <v>45400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>80300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>5100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-3500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3400</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>-400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2900</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>3400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>6600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>1900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-900</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>-100</v>
       </c>
       <c r="Z14" s="3">
         <v>-100</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
+      <c r="AA14" s="3">
+        <v>-100</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
@@ -1348,34 +1368,37 @@
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF14" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E15" s="3">
         <v>1900</v>
-      </c>
-      <c r="E15" s="3">
-        <v>2000</v>
       </c>
       <c r="F15" s="3">
         <v>2000</v>
       </c>
       <c r="G15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H15" s="3">
         <v>1900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2100</v>
-      </c>
-      <c r="J15" s="3">
-        <v>2200</v>
       </c>
       <c r="K15" s="3">
         <v>2200</v>
@@ -1384,64 +1407,67 @@
         <v>2200</v>
       </c>
       <c r="M15" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="N15" s="3">
         <v>2100</v>
       </c>
       <c r="O15" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="P15" s="3">
         <v>2200</v>
       </c>
       <c r="Q15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="R15" s="3">
         <v>2100</v>
-      </c>
-      <c r="R15" s="3">
-        <v>2000</v>
       </c>
       <c r="S15" s="3">
         <v>2000</v>
       </c>
       <c r="T15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="U15" s="3">
         <v>2200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>2400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>2500</v>
-      </c>
-      <c r="W15" s="3">
-        <v>2700</v>
       </c>
       <c r="X15" s="3">
         <v>2700</v>
       </c>
       <c r="Y15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="Z15" s="3">
         <v>2900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>2500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>2200</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>2100</v>
       </c>
       <c r="AC15" s="3">
         <v>2100</v>
       </c>
       <c r="AD15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AE15" s="3">
         <v>2000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>133400</v>
+      </c>
+      <c r="E17" s="3">
         <v>133700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>142100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>136600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>140400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>145200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>151400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>165300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>167800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>176700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>176900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>178900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>188900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>187100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>180500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>165100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>156900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>154600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>152000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>143100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>171100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>164600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>166800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>164200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>168300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>169300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>172500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>168800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>174300</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-4300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>11700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>16600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>10100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>23500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>25200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>28100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>17500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>19700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>18000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>15400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>4200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>7500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>17700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>8000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>13800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>10200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>16300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>9800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,20 +1714,21 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>-100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
@@ -1714,153 +1748,159 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="P20" s="3">
         <v>-300</v>
       </c>
       <c r="Q20" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="R20" s="3">
         <v>100</v>
       </c>
       <c r="S20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-300</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>100</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-500</v>
       </c>
       <c r="X20" s="3">
         <v>-500</v>
       </c>
       <c r="Y20" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="Z20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-2400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>9700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>8200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>13900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>7100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>18900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>12300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>25400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>27300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>29900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>19400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>21900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>20100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>17500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>3600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>6800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>9700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>5600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>20600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>10000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>16200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>12400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>18500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>11900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1885,15 +1925,15 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3">
         <v>-100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
       <c r="N22" s="3">
         <v>0</v>
       </c>
@@ -1915,8 +1955,8 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>8</v>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>8</v>
@@ -1933,14 +1973,14 @@
       <c r="Z22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB22" s="3">
         <v>600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>700</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>600</v>
       </c>
       <c r="AD22" s="3">
         <v>600</v>
@@ -1948,186 +1988,195 @@
       <c r="AE22" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-65300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-49600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-76400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>11500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>8600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>17200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>23300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>25100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>27800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>17200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>19900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>18100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>15400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>7000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>3000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>17700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>7600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>13400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>9600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>15700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>9200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-5600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-7700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5400</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>5900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>7000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-7800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>4000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>3800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>5100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-73300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-44100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-68700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-5700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>10500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>11800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>17400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>18100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>20500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>19400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>14300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>12900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>23200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>2300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>6900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>12300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>9400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>5800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>10600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>5700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-73300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-44100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-68700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>10500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>11800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>17400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>18100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>20500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>19400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>14300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>12900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>23200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>2300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>6900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>12300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>9400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>5800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>10600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>5700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2550,8 +2611,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2568,11 +2629,14 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,20 +2816,23 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
@@ -2782,153 +2852,159 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="P32" s="3">
         <v>300</v>
       </c>
       <c r="Q32" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="R32" s="3">
         <v>-100</v>
       </c>
       <c r="S32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>300</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
-      </c>
-      <c r="W32" s="3">
-        <v>500</v>
       </c>
       <c r="X32" s="3">
         <v>500</v>
       </c>
       <c r="Y32" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-73300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-44100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-68700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>10500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>11800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>17400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>18100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>20500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>19400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>14300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>12900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>23200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>2300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>4100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>6900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>12300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>4900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>9400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>5800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>10600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>5700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-73300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-44100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-68700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>10500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>11800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>17400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>18100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>20500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>19400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>14300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>12900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>23200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>2300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>4100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>6900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>12300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>4900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>9400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>5800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>10600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>5700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45808</v>
+      </c>
+      <c r="E38" s="2">
         <v>45710</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45619</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45528</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45437</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45346</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45255</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45164</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45073</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44982</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44891</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44800</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44709</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44618</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44528</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44436</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44345</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44254</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44163</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44072</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43981</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43883</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43792</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43701</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43610</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43519</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43428</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43337</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43246</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,97 +3351,101 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>86100</v>
+      </c>
+      <c r="E41" s="3">
         <v>72500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>78200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>89600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>108900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>113800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>95800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>112600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>116800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>103900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>89400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>72600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>104200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>82200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>70600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>61900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>74400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>84000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>97200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>114600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>95600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>35900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>43000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>45700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>43000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>48000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>40800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>27100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>56500</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3429,11 +3519,11 @@
         <v>0</v>
       </c>
       <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB42" s="3">
         <v>6000</v>
       </c>
-      <c r="AB42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC42" s="3" t="s">
         <v>8</v>
       </c>
@@ -3443,97 +3533,103 @@
       <c r="AE42" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>107300</v>
+      </c>
+      <c r="E43" s="3">
         <v>109800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>115000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>114600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>116100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>120200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>138200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>135100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>142100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>151600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>182700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>183900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>188300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>187700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>182600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>164600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>153600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>119900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>114300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>111000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>129200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>138000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>138700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>130300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>135500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>142000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>147600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>138600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>131200</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3564,8 +3660,8 @@
       <c r="L44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -3621,8 +3717,11 @@
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3635,14 +3734,14 @@
       <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G45" s="3">
-        <v>8900</v>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H45" s="3">
         <v>8900</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
+      <c r="I45" s="3">
+        <v>8900</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>8</v>
@@ -3653,154 +3752,160 @@
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>6600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>16000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7800</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>6700</v>
       </c>
       <c r="R45" s="3">
         <v>6700</v>
       </c>
       <c r="S45" s="3">
+        <v>6700</v>
+      </c>
+      <c r="T45" s="3">
         <v>7200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>8100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>7100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>6000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>6200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>8000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>7700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>7400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>7100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>8100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>7000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>6800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>203700</v>
+      </c>
+      <c r="E46" s="3">
         <v>195200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>201700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>211500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>240800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>251300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>242200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>253500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>264100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>262600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>278700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>262200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>308500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>277800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>260000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>233300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>235300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>212000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>218600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>231500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>231000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>182000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>189400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>183400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>191700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>198000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>195400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>172500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>194900</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3831,8 +3936,8 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3888,186 +3993,195 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E48" s="3">
         <v>28000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>29500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>26900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>15700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>17500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>28600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>30000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>31200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>32600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>35200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>36500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>35200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>38100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>40500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>42700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>45200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>49000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>52300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>56200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>57900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>63000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>65100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>66100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>26600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>25700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>23700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>22600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>68500</v>
+      </c>
+      <c r="E49" s="3">
         <v>118400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>182000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>243800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>242300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>242000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>241400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>226300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>224200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>222000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>222800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>223100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>225500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>232800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>234200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>235600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>237000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>237100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>237300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>234800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>234100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>235100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>236400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>242200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>205400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>206700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>207700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>209400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>210500</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,97 +4361,103 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3">
         <v>17700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1400</v>
-      </c>
-      <c r="I52" s="3">
-        <v>1600</v>
       </c>
       <c r="J52" s="3">
         <v>1600</v>
       </c>
       <c r="K52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="L52" s="3">
         <v>1800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>13800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>12300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>12200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>11000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>4700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>4600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>4500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>4000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4545,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>304700</v>
+      </c>
+      <c r="E54" s="3">
         <v>375600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>424900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>512900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>510900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>523200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>524900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>522400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>532000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>532300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>550500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>534000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>581500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>559700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>538200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>514600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>520600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>501600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>512000</v>
-      </c>
-      <c r="V54" s="3">
-        <v>529200</v>
       </c>
       <c r="W54" s="3">
         <v>529200</v>
       </c>
       <c r="X54" s="3">
+        <v>529200</v>
+      </c>
+      <c r="Y54" s="3">
         <v>486000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>496400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>496600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>428400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>435100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>431300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>408400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>432700</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,130 +4707,134 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E57" s="3">
         <v>13200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>14000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>15200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>17400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>17500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>15700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>16500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>16600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>13600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>17800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>15900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>18100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>16000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>17500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>20300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>15300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>15800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>18600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>20100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>22800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>21600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>22400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>22300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>22000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>23300</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E58" s="3">
         <v>5300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>7500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>7700</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -4755,263 +4889,272 @@
       <c r="AE58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E59" s="3">
         <v>10000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>9500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13400</v>
-      </c>
-      <c r="J59" s="3">
-        <v>10400</v>
       </c>
       <c r="K59" s="3">
         <v>10400</v>
       </c>
       <c r="L59" s="3">
+        <v>10400</v>
+      </c>
+      <c r="M59" s="3">
         <v>11100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>84400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>78900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>110700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>97900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>83200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>77200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>84900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>85900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>71300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>72800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>79100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>72200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>77900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>66300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>69800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>58900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>63300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>50600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>71200</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>75400</v>
+      </c>
+      <c r="E60" s="3">
         <v>74200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>73600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>74600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>72400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>84100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>86800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>83900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>97100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>102100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>101000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>91800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>124300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>115600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>99100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>95400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>100900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>103400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>91600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>88100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>94900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>90800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>97900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>89000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>91400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>81300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>85600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>72600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>94500</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>20200</v>
+      </c>
+      <c r="E61" s="3">
         <v>21300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>22400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>19300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>8600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>10300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>11500</v>
-      </c>
-      <c r="M61" s="3">
-        <v>20000</v>
       </c>
       <c r="N61" s="3">
         <v>20000</v>
       </c>
       <c r="O61" s="3">
-        <v>54000</v>
+        <v>20000</v>
       </c>
       <c r="P61" s="3">
         <v>54000</v>
       </c>
       <c r="Q61" s="3">
+        <v>54000</v>
+      </c>
+      <c r="R61" s="3">
         <v>44000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>33000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>43000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>53000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>68000</v>
-      </c>
-      <c r="V61" s="3">
-        <v>88000</v>
       </c>
       <c r="W61" s="3">
         <v>88000</v>
       </c>
       <c r="X61" s="3">
+        <v>88000</v>
+      </c>
+      <c r="Y61" s="3">
         <v>49000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>54000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>73000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>43000</v>
-      </c>
-      <c r="AB61" s="3">
-        <v>58000</v>
       </c>
       <c r="AC61" s="3">
         <v>58000</v>
@@ -5020,99 +5163,105 @@
         <v>58000</v>
       </c>
       <c r="AE61" s="3">
+        <v>58000</v>
+      </c>
+      <c r="AF61" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E62" s="3">
         <v>2200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2500</v>
-      </c>
-      <c r="H62" s="3">
-        <v>5300</v>
       </c>
       <c r="I62" s="3">
         <v>5300</v>
       </c>
       <c r="J62" s="3">
+        <v>5300</v>
+      </c>
+      <c r="K62" s="3">
         <v>3100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>27400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>30300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>30700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>33100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>41500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>45400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>47200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>37600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>45400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>43200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>42600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>43400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>44200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>46200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>11600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>12500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>10300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>9500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5533,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>97600</v>
+      </c>
+      <c r="E66" s="3">
         <v>97800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>99200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>105700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>92200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>108300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>111300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>103500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>117500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>125500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>148400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>142100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>209000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>202700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>184600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>173800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>191100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>194000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>205000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>219200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>225500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>183200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>196100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>208200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>146000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>151800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>153900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>140100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>163800</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6027,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-121600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-45900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>78000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>88600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>83000</v>
-      </c>
-      <c r="I72" s="3">
-        <v>85900</v>
       </c>
       <c r="J72" s="3">
         <v>85900</v>
       </c>
       <c r="K72" s="3">
+        <v>85900</v>
+      </c>
+      <c r="L72" s="3">
         <v>87600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>80700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>78600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>66100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>52700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>36900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>22200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>375400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>367200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>348700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>352700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>358300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>360500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>361000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>358500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>350700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>350200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>345000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>343800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>337400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>335700</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,97 +6395,103 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>207100</v>
+      </c>
+      <c r="E76" s="3">
         <v>277800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>325700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>407200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>418800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>414900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>413600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>418800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>414500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>406800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>402100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>392000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>372400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>357000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>353600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>340800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>329500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>307600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>306900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>309900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>303700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>302800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>300300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>288400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>282400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>283300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>277400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>268300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>268800</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45808</v>
+      </c>
+      <c r="E80" s="2">
         <v>45710</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45619</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45528</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45437</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45346</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45255</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45164</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45073</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44982</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44891</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44800</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44709</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44618</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44528</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44436</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44345</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44254</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44163</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44072</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43981</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43883</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43792</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43701</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43610</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43519</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43428</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43337</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43246</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-73300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-44100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-68700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>10500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>11800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>17400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>18100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>20500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>19400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>14300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>12900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>23200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>2300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>4100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>6900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>12300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>4900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>9400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>5800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>10600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>5700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,19 +6804,20 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>600</v>
+      </c>
+      <c r="E83" s="3">
         <v>700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>800</v>
-      </c>
-      <c r="F83" s="3">
-        <v>900</v>
       </c>
       <c r="G83" s="3">
         <v>900</v>
@@ -6639,64 +6838,67 @@
         <v>900</v>
       </c>
       <c r="M83" s="3">
-        <v>2100</v>
+        <v>900</v>
       </c>
       <c r="N83" s="3">
         <v>2100</v>
       </c>
       <c r="O83" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="P83" s="3">
         <v>2200</v>
       </c>
       <c r="Q83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="R83" s="3">
         <v>2100</v>
-      </c>
-      <c r="R83" s="3">
-        <v>2000</v>
       </c>
       <c r="S83" s="3">
         <v>2000</v>
       </c>
       <c r="T83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="U83" s="3">
         <v>2200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>2400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>2500</v>
-      </c>
-      <c r="W83" s="3">
-        <v>2700</v>
       </c>
       <c r="X83" s="3">
         <v>2700</v>
       </c>
       <c r="Y83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="Z83" s="3">
         <v>2900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>2500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>2200</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>2100</v>
       </c>
       <c r="AC83" s="3">
         <v>2100</v>
       </c>
       <c r="AD83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AE83" s="3">
         <v>2000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7354,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E89" s="3">
         <v>700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>20500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>17800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>40200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>29000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>26800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>19200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>5800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>11000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>18600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>28000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>4300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>20300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>30100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>11800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>18300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-16600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,55 +7482,56 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-100</v>
       </c>
       <c r="H91" s="3">
         <v>-100</v>
       </c>
       <c r="I91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="J91" s="3">
         <v>-300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-700</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-300</v>
       </c>
       <c r="P91" s="3">
         <v>-300</v>
       </c>
       <c r="Q91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R91" s="3">
         <v>-1300</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-1000</v>
       </c>
       <c r="S91" s="3">
         <v>-1000</v>
@@ -7319,40 +7540,43 @@
         <v>-1000</v>
       </c>
       <c r="U91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="V91" s="3">
         <v>-1500</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-300</v>
       </c>
       <c r="W91" s="3">
         <v>-300</v>
       </c>
       <c r="X91" s="3">
-        <v>-800</v>
+        <v>-300</v>
       </c>
       <c r="Y91" s="3">
         <v>-800</v>
       </c>
       <c r="Z91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,97 +7756,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>2400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>2300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1300</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-1000</v>
       </c>
       <c r="S94" s="3">
         <v>-1000</v>
       </c>
       <c r="T94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="U94" s="3">
         <v>-1200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-24800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-6900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7660,7 +7894,7 @@
         <v>4600</v>
       </c>
       <c r="E96" s="3">
-        <v>4700</v>
+        <v>4600</v>
       </c>
       <c r="F96" s="3">
         <v>4700</v>
@@ -7684,19 +7918,19 @@
         <v>4700</v>
       </c>
       <c r="M96" s="3">
+        <v>4700</v>
+      </c>
+      <c r="N96" s="3">
         <v>-4700</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-4600</v>
       </c>
       <c r="O96" s="3">
         <v>-4600</v>
       </c>
       <c r="P96" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-4700</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-4600</v>
       </c>
       <c r="R96" s="3">
         <v>-4600</v>
@@ -7708,7 +7942,7 @@
         <v>-4600</v>
       </c>
       <c r="U96" s="3">
-        <v>-4500</v>
+        <v>-4600</v>
       </c>
       <c r="V96" s="3">
         <v>-4500</v>
@@ -7723,7 +7957,7 @@
         <v>-4500</v>
       </c>
       <c r="Z96" s="3">
-        <v>-4100</v>
+        <v>-4500</v>
       </c>
       <c r="AA96" s="3">
         <v>-4100</v>
@@ -7735,13 +7969,16 @@
         <v>-4100</v>
       </c>
       <c r="AD96" s="3">
-        <v>-3800</v>
+        <v>-4100</v>
       </c>
       <c r="AE96" s="3">
         <v>-3800</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>-3800</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,271 +8250,283 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-9700</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-7700</v>
       </c>
       <c r="G100" s="3">
         <v>-7700</v>
       </c>
       <c r="H100" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="I100" s="3">
         <v>-1700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-9700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-7600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-25900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-9300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-29100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>8100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-11400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-13500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-16900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-27600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>32700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-10300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-22300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>30700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-28000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-11700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-4800</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-2300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>2100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-100</v>
       </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-19300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>18100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-16800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>12900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>14500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>16900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-31600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>22300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>11600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>8700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-12500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-9600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-13200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-17400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>18900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>59700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-7100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-4900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>7100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>13800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-29400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>13300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RGP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RGP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="92">
   <si>
     <t>RGP</t>
   </si>
@@ -656,429 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45990</v>
+      </c>
+      <c r="E7" s="2">
         <v>45899</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45808</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45710</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45619</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45528</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45437</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45346</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45255</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45164</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45073</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44982</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44891</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44800</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44709</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44618</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44528</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44436</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44345</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44254</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44163</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44072</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43981</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43883</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43792</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43701</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43610</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43519</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43428</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43337</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43246</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>117700</v>
+      </c>
+      <c r="E8" s="3">
         <v>120200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>139300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>129400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>145600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>136900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>148200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>151300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>163100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>170200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>184400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>186800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>200400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>204100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>217000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>204600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>200200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>183100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>172300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>156600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>153200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>147300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>178600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>168100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>184500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>172200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>182100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>179500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>188800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>178600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>183800</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E9" s="3">
         <v>72800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>83400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>84100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>89500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>86900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>88600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>95300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>99700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>103200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>108700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>115200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>118000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>120600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>127400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>127800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>121500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>111700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>104000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>99600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>95000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>89400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>106400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>106600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>110100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>104700</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>109200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>111600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>115400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>110400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>113400</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E10" s="3">
         <v>47500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>56000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>45400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>56100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>50000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>59600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>56000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>63500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>67000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>75700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>71600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>82400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>83500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>89600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>76800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>78700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>71400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>68300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>57000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>58200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>57900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>72200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>61500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>74400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>67500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>72900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>67900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>73400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>68200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>70400</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1112,16 +1124,17 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
         <v>700</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
+      <c r="E12" s="3">
+        <v>700</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -1207,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1302,88 +1318,91 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E14" s="3">
         <v>400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>71400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>45400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>80300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>5100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-3500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3400</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>-400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2900</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>400</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>3400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>6600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>-900</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>-100</v>
       </c>
       <c r="AB14" s="3">
         <v>-100</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
+      <c r="AC14" s="3">
+        <v>-100</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
@@ -1394,11 +1413,14 @@
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1406,28 +1428,28 @@
         <v>1500</v>
       </c>
       <c r="E15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F15" s="3">
         <v>1800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1900</v>
-      </c>
-      <c r="G15" s="3">
-        <v>2000</v>
       </c>
       <c r="H15" s="3">
         <v>2000</v>
       </c>
       <c r="I15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="J15" s="3">
         <v>1900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2100</v>
-      </c>
-      <c r="L15" s="3">
-        <v>2200</v>
       </c>
       <c r="M15" s="3">
         <v>2200</v>
@@ -1436,64 +1458,67 @@
         <v>2200</v>
       </c>
       <c r="O15" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="P15" s="3">
         <v>2100</v>
       </c>
       <c r="Q15" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="R15" s="3">
         <v>2200</v>
       </c>
       <c r="S15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="T15" s="3">
         <v>2100</v>
-      </c>
-      <c r="T15" s="3">
-        <v>2000</v>
       </c>
       <c r="U15" s="3">
         <v>2000</v>
       </c>
       <c r="V15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="W15" s="3">
         <v>2200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2500</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>2700</v>
       </c>
       <c r="Z15" s="3">
         <v>2700</v>
       </c>
       <c r="AA15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AB15" s="3">
         <v>2900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>2500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>2200</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>2100</v>
       </c>
       <c r="AE15" s="3">
         <v>2100</v>
       </c>
       <c r="AF15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AG15" s="3">
         <v>2000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1524,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>117500</v>
+      </c>
+      <c r="E17" s="3">
         <v>121800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>133400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>133700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>142100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>136600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>140400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>145200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>151400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>165300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>167800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>176700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>176900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>178900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>188900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>187100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>180500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>165100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>156900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>154600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>152000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>143100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>171100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>164600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>166800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>164200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>168300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>169300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>172500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>168800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>174300</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-1600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>3600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>7800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>11700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>16600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>10100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>23500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>25200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>28100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>17500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>19700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>18000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>15400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>7500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>17700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>8000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>13800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>10200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>16300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>9800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1749,26 +1781,27 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
         <v>-100</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>-100</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
@@ -1788,167 +1821,173 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-200</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="R20" s="3">
         <v>-300</v>
       </c>
       <c r="S20" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="T20" s="3">
         <v>100</v>
       </c>
       <c r="U20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-300</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>100</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-500</v>
       </c>
       <c r="Z20" s="3">
         <v>-500</v>
       </c>
       <c r="AA20" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>100</v>
       </c>
-      <c r="AE20" s="3">
-        <v>0</v>
-      </c>
       <c r="AF20" s="3">
         <v>0</v>
       </c>
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E21" s="3">
         <v>100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>7800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-2400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>9700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>13900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>18900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>12300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>25400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>27300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>29900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>19400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>21900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>20100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>17500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>3900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>3600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>6800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>9700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>5600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>20600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>10000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>16200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>12400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>18500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>11900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>8</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>8</v>
@@ -1971,15 +2010,15 @@
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="3">
         <v>-100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>100</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
         <v>0</v>
       </c>
@@ -2001,8 +2040,8 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>8</v>
+      <c r="W22" s="3">
+        <v>0</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>8</v>
@@ -2019,14 +2058,14 @@
       <c r="AB22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AC22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD22" s="3">
         <v>600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>700</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>600</v>
       </c>
       <c r="AF22" s="3">
         <v>600</v>
@@ -2034,198 +2073,207 @@
       <c r="AG22" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-65300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-49600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-76400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-4700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>11500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>8600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>17200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>23300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>25100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>27800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>17200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>19900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>18100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>15400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>4200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>7000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>17700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>7600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>13400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>9600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>15700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>9200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>700</v>
+      </c>
+      <c r="E24" s="3">
         <v>500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-5600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-7700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5400</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>5900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>7000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-2200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-7800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>4000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>5100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2319,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-73300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-44100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-68700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>10500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>11800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>17400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>18100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>20500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>19400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>14300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>12900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>23200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>2300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>6900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>12300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>9400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>5800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>10600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>5700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-2400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-73300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-44100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-68700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>10500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>11800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>17400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>18100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>20500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>19400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>14300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>12900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>23200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>2300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>6900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>12300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>4900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>9400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>5800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>10600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>5700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2604,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2678,8 +2738,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2696,11 +2756,14 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2794,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2889,26 +2955,29 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
         <v>100</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>100</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
@@ -2928,159 +2997,165 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>200</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="R32" s="3">
         <v>300</v>
       </c>
       <c r="S32" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="T32" s="3">
         <v>-100</v>
       </c>
       <c r="U32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>300</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-100</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>500</v>
       </c>
       <c r="Z32" s="3">
         <v>500</v>
       </c>
       <c r="AA32" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-100</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
         <v>0</v>
       </c>
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-2400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-73300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-44100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-68700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>10500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>11800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>17400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>18100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>20500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>19400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>14300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>12900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>23200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>2300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>6900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>12300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>4900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>9400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>5800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>10600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>5700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3174,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-2400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-73300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-44100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-68700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>10500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>11800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>17400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>18100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>20500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>19400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>14300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>12900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>23200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>2300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>6900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>12300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>4900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>9400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>5800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>10600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>5700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45990</v>
+      </c>
+      <c r="E38" s="2">
         <v>45899</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45808</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45710</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45619</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45528</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45437</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45346</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45255</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45164</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45073</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44982</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44891</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44800</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44709</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44618</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44528</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44436</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44345</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44254</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44163</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44072</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43981</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43883</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43792</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43701</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43610</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43519</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43428</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43337</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43246</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3404,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3439,103 +3524,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>89800</v>
+      </c>
+      <c r="E41" s="3">
         <v>77500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>86100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>72500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>78200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>89600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>108900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>113800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>95800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>112600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>116800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>103900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>89400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>72600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>104200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>82200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>70600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>61900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>74400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>84000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>97200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>114600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>95600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>35900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>43000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>45700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>43000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>48000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>40800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>27100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>56500</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3615,11 +3704,11 @@
         <v>0</v>
       </c>
       <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="3">
         <v>6000</v>
       </c>
-      <c r="AD42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE42" s="3" t="s">
         <v>8</v>
       </c>
@@ -3629,103 +3718,109 @@
       <c r="AG42" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>94100</v>
+      </c>
+      <c r="E43" s="3">
         <v>101300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>107300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>109800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>115000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>114600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>116100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>120200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>138200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>135100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>142100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>151600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>182700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>183900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>188300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>187700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>182600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>164600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>153600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>119900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>114300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>111000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>129200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>138000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>138700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>130300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>135500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>142000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>147600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>138600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>131200</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3762,8 +3857,8 @@
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3819,8 +3914,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3839,14 +3937,14 @@
       <c r="H45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I45" s="3">
-        <v>8900</v>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J45" s="3">
         <v>8900</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>8</v>
+      <c r="K45" s="3">
+        <v>8900</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>8</v>
@@ -3857,160 +3955,166 @@
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3">
         <v>6600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>16000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>7800</v>
-      </c>
-      <c r="S45" s="3">
-        <v>6700</v>
       </c>
       <c r="T45" s="3">
         <v>6700</v>
       </c>
       <c r="U45" s="3">
+        <v>6700</v>
+      </c>
+      <c r="V45" s="3">
         <v>7200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>8100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>7100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>6000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>6200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>8000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>7700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>7400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>7100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>8100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>7000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>6800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>193200</v>
+      </c>
+      <c r="E46" s="3">
         <v>188200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>203700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>195200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>201700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>211500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>240800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>251300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>242200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>253500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>264100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>262600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>278700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>262200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>308500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>277800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>260000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>233300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>235300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>212000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>218600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>231500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>231000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>182000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>189400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>183400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>191700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>198000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>195400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>172500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>194900</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4047,8 +4151,8 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4104,198 +4208,207 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>25700</v>
+      </c>
+      <c r="E48" s="3">
         <v>26600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>27000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>28000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>29500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>26900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>15700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>17500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>28600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>30000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>31200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>32600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>35200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>36500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>35200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>38100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>40500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>42700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>45200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>49000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>52300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>56200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>57900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>63000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>65100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>66100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>26600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>25700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>23700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>22600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>45400</v>
+      </c>
+      <c r="E49" s="3">
         <v>46500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>68500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>118400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>182000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>243800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>242300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>242000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>241400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>226300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>224200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>222000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>222800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>223100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>225500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>232800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>234200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>235600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>237000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>237100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>237300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>234800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>234100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>235100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>236400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>242200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>205400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>206700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>207700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>209400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>210500</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4389,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4484,103 +4600,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E52" s="3">
         <v>16300</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3">
         <v>17700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1400</v>
-      </c>
-      <c r="K52" s="3">
-        <v>1600</v>
       </c>
       <c r="L52" s="3">
         <v>1600</v>
       </c>
       <c r="M52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="N52" s="3">
         <v>1800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>13800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>12300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>12200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>11000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>4700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>4600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>4500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>4000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4674,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>289300</v>
+      </c>
+      <c r="E54" s="3">
         <v>287200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>304700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>375600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>424900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>512900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>510900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>523200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>524900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>522400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>532000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>532300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>550500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>534000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>581500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>559700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>538200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>514600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>520600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>501600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>512000</v>
-      </c>
-      <c r="X54" s="3">
-        <v>529200</v>
       </c>
       <c r="Y54" s="3">
         <v>529200</v>
       </c>
       <c r="Z54" s="3">
+        <v>529200</v>
+      </c>
+      <c r="AA54" s="3">
         <v>486000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>496400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>496600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>428400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>435100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>431300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>408400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>432700</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4804,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4839,142 +4968,146 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E57" s="3">
         <v>12400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>14000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>15200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>17400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>17500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>15700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>16500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>16600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>12900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>13600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>17800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>15900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>18100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>16000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>17500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>20300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>15300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>15800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>18600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>20100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>22800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>21600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>22400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>22300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>22000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>23300</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5100</v>
+        <v>4900</v>
       </c>
       <c r="E58" s="3">
         <v>5100</v>
       </c>
       <c r="F58" s="3">
+        <v>5100</v>
+      </c>
+      <c r="G58" s="3">
         <v>5300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>7500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7700</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -5029,281 +5162,290 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E59" s="3">
         <v>8900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>10000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>10500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13400</v>
-      </c>
-      <c r="L59" s="3">
-        <v>10400</v>
       </c>
       <c r="M59" s="3">
         <v>10400</v>
       </c>
       <c r="N59" s="3">
+        <v>10400</v>
+      </c>
+      <c r="O59" s="3">
         <v>11100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>84400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>78900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>110700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>97900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>83200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>77200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>84900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>85900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>71300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>72800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>79100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>72200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>77900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>66300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>69800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>58900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>63300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>50600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>71200</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>73100</v>
+      </c>
+      <c r="E60" s="3">
         <v>58600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>75400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>74200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>73600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>74600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>72400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>84100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>86800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>83900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>97100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>102100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>101000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>91800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>124300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>115600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>99100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>95400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>100900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>103400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>91600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>88100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>94900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>90800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>97900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>89000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>91400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>81300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>85600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>72600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>94500</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>20200</v>
+        <v>19800</v>
       </c>
       <c r="E61" s="3">
         <v>20200</v>
       </c>
       <c r="F61" s="3">
+        <v>20200</v>
+      </c>
+      <c r="G61" s="3">
         <v>21300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>22400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>19300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11500</v>
-      </c>
-      <c r="O61" s="3">
-        <v>20000</v>
       </c>
       <c r="P61" s="3">
         <v>20000</v>
       </c>
       <c r="Q61" s="3">
-        <v>54000</v>
+        <v>20000</v>
       </c>
       <c r="R61" s="3">
         <v>54000</v>
       </c>
       <c r="S61" s="3">
+        <v>54000</v>
+      </c>
+      <c r="T61" s="3">
         <v>44000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>33000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>43000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>53000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>68000</v>
-      </c>
-      <c r="X61" s="3">
-        <v>88000</v>
       </c>
       <c r="Y61" s="3">
         <v>88000</v>
       </c>
       <c r="Z61" s="3">
+        <v>88000</v>
+      </c>
+      <c r="AA61" s="3">
         <v>49000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>54000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>73000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>43000</v>
-      </c>
-      <c r="AD61" s="3">
-        <v>58000</v>
       </c>
       <c r="AE61" s="3">
         <v>58000</v>
@@ -5312,105 +5454,111 @@
         <v>58000</v>
       </c>
       <c r="AG61" s="3">
+        <v>58000</v>
+      </c>
+      <c r="AH61" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="E62" s="3">
         <v>2000</v>
       </c>
       <c r="F62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G62" s="3">
         <v>2200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2500</v>
-      </c>
-      <c r="J62" s="3">
-        <v>5300</v>
       </c>
       <c r="K62" s="3">
         <v>5300</v>
       </c>
       <c r="L62" s="3">
+        <v>5300</v>
+      </c>
+      <c r="M62" s="3">
         <v>3100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>27400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>30300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>30700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>33100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>41500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>45400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>47200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>37600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>45400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>43200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>42600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>43400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>44200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>46200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>11600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>12500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>10300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>9500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5504,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5599,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5694,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>94700</v>
+      </c>
+      <c r="E66" s="3">
         <v>80900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>97600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>97800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>99200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>105700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>92200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>108300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>111300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>103500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>117500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>125500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>148400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>142100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>209000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>202700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>184600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>173800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>191100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>194000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>205000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>219200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>225500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>183200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>196100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>208200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>146000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>151800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>153900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>140100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>163800</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5824,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5919,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6014,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6109,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6204,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-141700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-126900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-121600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-45900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>78000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>88600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>83000</v>
-      </c>
-      <c r="K72" s="3">
-        <v>85900</v>
       </c>
       <c r="L72" s="3">
         <v>85900</v>
       </c>
       <c r="M72" s="3">
+        <v>85900</v>
+      </c>
+      <c r="N72" s="3">
         <v>87600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>80700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>78600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>66100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>52700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>36900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>22200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>375400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>367200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>348700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>352700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>358300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>360500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>361000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>358500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>350700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>350200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>345000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>343800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>337400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>335700</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6394,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6489,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6584,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>194600</v>
+      </c>
+      <c r="E76" s="3">
         <v>206400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>207100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>277800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>325700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>407200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>418800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>414900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>413600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>418800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>414500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>406800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>402100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>392000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>372400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>357000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>353600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>340800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>329500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>307600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>306900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>309900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>303700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>302800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>300300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>288400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>282400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>283300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>277400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>268300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>268800</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6774,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45990</v>
+      </c>
+      <c r="E80" s="2">
         <v>45899</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45808</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45710</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45619</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45528</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45437</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45346</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45255</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45164</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45073</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44982</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44891</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44800</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44709</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44618</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44528</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44436</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44345</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44254</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44163</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44072</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43981</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43883</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43792</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43701</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43610</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43519</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43428</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43337</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43246</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-12700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-2400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-73300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-44100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-68700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>10500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>11800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>17400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>18100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>20500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>19400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>14300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>12900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>23200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>2300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>6900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>12300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>4900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>9400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>5800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>10600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>5700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7004,25 +7201,26 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E83" s="3">
         <v>2000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>800</v>
-      </c>
-      <c r="H83" s="3">
-        <v>900</v>
       </c>
       <c r="I83" s="3">
         <v>900</v>
@@ -7043,64 +7241,67 @@
         <v>900</v>
       </c>
       <c r="O83" s="3">
-        <v>2100</v>
+        <v>900</v>
       </c>
       <c r="P83" s="3">
         <v>2100</v>
       </c>
       <c r="Q83" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="R83" s="3">
         <v>2200</v>
       </c>
       <c r="S83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="T83" s="3">
         <v>2100</v>
-      </c>
-      <c r="T83" s="3">
-        <v>2000</v>
       </c>
       <c r="U83" s="3">
         <v>2000</v>
       </c>
       <c r="V83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="W83" s="3">
         <v>2200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>2400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2500</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>2700</v>
       </c>
       <c r="Z83" s="3">
         <v>2700</v>
       </c>
       <c r="AA83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AB83" s="3">
         <v>2900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>2500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>2200</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>2100</v>
       </c>
       <c r="AE83" s="3">
         <v>2100</v>
       </c>
       <c r="AF83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AG83" s="3">
         <v>2000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7194,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7289,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7384,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7479,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7574,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>16800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>20500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>17800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>40200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>29000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>26800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>19200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>3000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>5800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>11000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>18600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>28000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>4300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>20300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>30100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>11800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>18300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-16600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7704,61 +7923,62 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-300</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-100</v>
       </c>
       <c r="J91" s="3">
         <v>-100</v>
       </c>
       <c r="K91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L91" s="3">
         <v>-300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-700</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-300</v>
       </c>
       <c r="R91" s="3">
         <v>-300</v>
       </c>
       <c r="S91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="T91" s="3">
         <v>-1300</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-1000</v>
       </c>
       <c r="U91" s="3">
         <v>-1000</v>
@@ -7767,40 +7987,43 @@
         <v>-1000</v>
       </c>
       <c r="W91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="X91" s="3">
         <v>-1500</v>
-      </c>
-      <c r="X91" s="3">
-        <v>-300</v>
       </c>
       <c r="Y91" s="3">
         <v>-300</v>
       </c>
       <c r="Z91" s="3">
-        <v>-800</v>
+        <v>-300</v>
       </c>
       <c r="AA91" s="3">
         <v>-800</v>
       </c>
       <c r="AB91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7894,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7989,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-10900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>2400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>2300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1300</v>
-      </c>
-      <c r="T94" s="3">
-        <v>-1000</v>
       </c>
       <c r="U94" s="3">
         <v>-1000</v>
       </c>
       <c r="V94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="W94" s="3">
         <v>-1200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-24800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-6900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8119,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8128,13 +8361,13 @@
         <v>2300</v>
       </c>
       <c r="E96" s="3">
-        <v>4600</v>
+        <v>2300</v>
       </c>
       <c r="F96" s="3">
         <v>4600</v>
       </c>
       <c r="G96" s="3">
-        <v>4700</v>
+        <v>4600</v>
       </c>
       <c r="H96" s="3">
         <v>4700</v>
@@ -8158,19 +8391,19 @@
         <v>4700</v>
       </c>
       <c r="O96" s="3">
+        <v>4700</v>
+      </c>
+      <c r="P96" s="3">
         <v>-4700</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-4600</v>
       </c>
       <c r="Q96" s="3">
         <v>-4600</v>
       </c>
       <c r="R96" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="S96" s="3">
         <v>-4700</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-4600</v>
       </c>
       <c r="T96" s="3">
         <v>-4600</v>
@@ -8182,7 +8415,7 @@
         <v>-4600</v>
       </c>
       <c r="W96" s="3">
-        <v>-4500</v>
+        <v>-4600</v>
       </c>
       <c r="X96" s="3">
         <v>-4500</v>
@@ -8197,7 +8430,7 @@
         <v>-4500</v>
       </c>
       <c r="AB96" s="3">
-        <v>-4100</v>
+        <v>-4500</v>
       </c>
       <c r="AC96" s="3">
         <v>-4100</v>
@@ -8209,13 +8442,16 @@
         <v>-4100</v>
       </c>
       <c r="AF96" s="3">
-        <v>-3800</v>
+        <v>-4100</v>
       </c>
       <c r="AG96" s="3">
         <v>-3800</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>-3800</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8309,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8404,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8499,289 +8741,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-9700</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-7700</v>
       </c>
       <c r="I100" s="3">
         <v>-7700</v>
       </c>
       <c r="J100" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-9700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-7600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-25900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-9300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-29100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-2900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-7100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>8100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-11400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-13500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-16900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-27600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>32700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-10300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-22300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>30700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-28000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-11700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-4800</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-300</v>
+        <v>-1800</v>
       </c>
       <c r="E101" s="3">
         <v>-300</v>
       </c>
       <c r="F101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="G101" s="3">
         <v>-400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-1100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>2100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-100</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-8600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>13700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-19300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>18100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-16800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-4200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>12900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>14500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>16900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-31600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>22300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>11600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>8700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-12500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-9600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-13200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-17400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>18900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>59700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-7100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>2700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-4900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>7100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>13800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-29400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>13300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RGP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RGP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="92">
   <si>
     <t>RGP</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="15.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="15.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E7" s="2">
         <v>45990</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45899</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45808</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45710</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45619</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45528</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45437</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45346</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45255</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45164</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45073</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44982</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44891</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44800</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44709</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44618</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44528</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44436</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44345</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44254</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44163</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44072</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43981</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43883</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43792</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43701</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43610</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43519</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43428</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43337</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43246</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>107900</v>
+      </c>
+      <c r="E8" s="3">
         <v>117700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>120200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>139300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>129400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>145600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>136900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>148200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>151300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>163100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>170200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>184400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>186800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>200400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>204100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>217000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>204600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>200200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>183100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>172300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>156600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>153200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>147300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>178600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>168100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>184500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>172200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>182100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>179500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>188800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>178600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>183800</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>69400</v>
+      </c>
+      <c r="E9" s="3">
         <v>74000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>72800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>83400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>84100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>89500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>86900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>88600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>95300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>99700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>103200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>108700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>115200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>118000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>120600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>127400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>127800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>121500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>111700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>104000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>99600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>95000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>89400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>106400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>106600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>110100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>104700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>109200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>111600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>115400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>110400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>113400</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E10" s="3">
         <v>43700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>47500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>56000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>45400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>56100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>50000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>59600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>56000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>63500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>67000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>75700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>71600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>82400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>83500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>89600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>76800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>78700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>71400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>68300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>57000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>58200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>57900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>72200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>61500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>74400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>67500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>72900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>67900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>73400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>68200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>70400</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1136,14 +1150,14 @@
       <c r="E12" s="3">
         <v>700</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
+      <c r="F12" s="3">
+        <v>700</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
+      <c r="H12" s="3">
+        <v>600</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>8</v>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,91 +1338,94 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E14" s="3">
         <v>12400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>71400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>45400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>80300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>5100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-3500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3400</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>-400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2900</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>1300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>3400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>6600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>1500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>1900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-900</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>-100</v>
       </c>
       <c r="AC14" s="3">
         <v>-100</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
+      <c r="AD14" s="3">
+        <v>-100</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
@@ -1416,43 +1436,46 @@
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI14" s="3">
         <v>3700</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1500</v>
+        <v>1100</v>
       </c>
       <c r="E15" s="3">
         <v>1500</v>
       </c>
       <c r="F15" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G15" s="3">
         <v>1800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1900</v>
-      </c>
-      <c r="H15" s="3">
-        <v>2000</v>
       </c>
       <c r="I15" s="3">
         <v>2000</v>
       </c>
       <c r="J15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K15" s="3">
         <v>1900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2100</v>
-      </c>
-      <c r="M15" s="3">
-        <v>2200</v>
       </c>
       <c r="N15" s="3">
         <v>2200</v>
@@ -1461,64 +1484,67 @@
         <v>2200</v>
       </c>
       <c r="P15" s="3">
-        <v>2100</v>
+        <v>2200</v>
       </c>
       <c r="Q15" s="3">
         <v>2100</v>
       </c>
       <c r="R15" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="S15" s="3">
         <v>2200</v>
       </c>
       <c r="T15" s="3">
+        <v>2200</v>
+      </c>
+      <c r="U15" s="3">
         <v>2100</v>
-      </c>
-      <c r="U15" s="3">
-        <v>2000</v>
       </c>
       <c r="V15" s="3">
         <v>2000</v>
       </c>
       <c r="W15" s="3">
+        <v>2000</v>
+      </c>
+      <c r="X15" s="3">
         <v>2200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>2400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2500</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>2700</v>
       </c>
       <c r="AA15" s="3">
         <v>2700</v>
       </c>
       <c r="AB15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AC15" s="3">
         <v>2900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>2500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>2200</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>2100</v>
       </c>
       <c r="AF15" s="3">
         <v>2100</v>
       </c>
       <c r="AG15" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AH15" s="3">
         <v>2000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>111600</v>
+      </c>
+      <c r="E17" s="3">
         <v>117500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>121800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>133400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>133700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>142100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>136600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>140400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>145200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>151400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>165300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>167800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>176700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>176900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>178900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>188900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>187100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>180500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>165100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>156900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>154600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>152000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>143100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>171100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>164600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>166800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>164200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>168300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>169300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>172500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>168800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>174300</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E18" s="3">
         <v>200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-1600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>5900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-4300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>11700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>16600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>10100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>23500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>25200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>28100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>17500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>19700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>18000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>15400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>2000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>7500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>17700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>8000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>13800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>10200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>16300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>9800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,29 +1815,30 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
         <v>-100</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>-100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
@@ -1824,173 +1858,179 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="S20" s="3">
         <v>-300</v>
       </c>
       <c r="T20" s="3">
-        <v>100</v>
+        <v>-300</v>
       </c>
       <c r="U20" s="3">
         <v>100</v>
       </c>
       <c r="V20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-300</v>
       </c>
-      <c r="X20" s="3">
-        <v>0</v>
-      </c>
       <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3">
         <v>100</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-500</v>
       </c>
       <c r="AA20" s="3">
         <v>-500</v>
       </c>
       <c r="AB20" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>100</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
       <c r="AG20" s="3">
         <v>0</v>
       </c>
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E21" s="3">
         <v>1700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>7800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-2400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>13900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>18900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>12300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>25400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>27300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>29900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>19400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>21900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>20100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>17500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>3900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>3600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>6800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>9700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>5600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>20600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>10000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>16200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>12400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>18500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>11900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>11600</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>8</v>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>8</v>
@@ -2013,15 +2053,15 @@
       <c r="M22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="3">
         <v>-100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>100</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
         <v>0</v>
       </c>
@@ -2043,8 +2083,8 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>8</v>
+      <c r="X22" s="3">
+        <v>0</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>8</v>
@@ -2061,14 +2101,14 @@
       <c r="AC22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AD22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE22" s="3">
         <v>600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>700</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>600</v>
       </c>
       <c r="AG22" s="3">
         <v>600</v>
@@ -2076,106 +2116,112 @@
       <c r="AH22" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-11900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-65300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-49600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-76400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-4700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>11500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>8600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>17200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>7000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>23300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>25100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>27800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>17200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>19900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>18100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>15400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>7000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>17700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>7600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>13400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>9600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>15700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>9200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2183,97 +2229,100 @@
         <v>700</v>
       </c>
       <c r="E24" s="3">
+        <v>700</v>
+      </c>
+      <c r="F24" s="3">
         <v>500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-5600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-7700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5400</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>5900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-2200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-7800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>2000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>5300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>2600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>4000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>3800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>5100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>4600</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-12700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-73300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-44100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-68700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>10500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>11800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>17400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>18100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>20500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>19400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>14300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>12900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>23200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>2300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>6900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>12300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>9400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>5800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>10600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>5700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-12700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-2400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-73300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-44100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-68700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-5700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>10500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>11800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>17400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>18100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>20500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>19400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>14300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>12900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>23200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>2300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>6900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>12300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>4900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>9400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>5800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>10600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>5700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>4300</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2741,8 +2802,8 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2759,11 +2820,14 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI29" s="3">
         <v>-300</v>
       </c>
     </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,29 +3025,32 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-600</v>
       </c>
       <c r="E32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
         <v>100</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
@@ -3000,162 +3070,168 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="S32" s="3">
         <v>300</v>
       </c>
       <c r="T32" s="3">
-        <v>-100</v>
+        <v>300</v>
       </c>
       <c r="U32" s="3">
         <v>-100</v>
       </c>
       <c r="V32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>300</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-100</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>500</v>
       </c>
       <c r="AA32" s="3">
         <v>500</v>
       </c>
       <c r="AB32" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-100</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
       <c r="AG32" s="3">
         <v>0</v>
       </c>
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-12700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-2400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-73300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-44100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-68700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-5700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>10500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>11800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>17400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>18100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>20500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>19400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>14300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>12900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>23200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>2300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>4100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>6900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>12300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>4900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>9400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>5800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>10600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>5700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-12700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-2400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-73300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-44100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-68700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-5700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>10500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>11800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>17400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>18100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>20500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>19400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>14300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>12900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>23200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>2300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>4100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>6900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>12300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>4900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>9400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>5800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>10600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>5700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E38" s="2">
         <v>45990</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45899</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45808</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45710</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45619</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45528</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45437</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45346</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45255</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45164</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45073</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44982</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44891</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44800</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44709</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44618</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44528</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44436</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44345</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44254</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44163</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44072</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43981</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43883</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43792</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43701</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43610</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43519</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43428</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43337</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43246</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>82800</v>
+      </c>
+      <c r="E41" s="3">
         <v>89800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>77500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>86100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>72500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>78200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>89600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>108900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>113800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>95800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>112600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>116800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>103900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>89400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>72600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>104200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>82200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>70600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>61900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>74400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>84000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>97200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>114600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>95600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>35900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>43000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>45700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>43000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>48000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>40800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>27100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>56500</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3707,11 +3797,11 @@
         <v>0</v>
       </c>
       <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="3">
         <v>6000</v>
       </c>
-      <c r="AE42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF42" s="3" t="s">
         <v>8</v>
       </c>
@@ -3721,106 +3811,112 @@
       <c r="AH42" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>87000</v>
+      </c>
+      <c r="E43" s="3">
         <v>94100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>101300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>107300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>109800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>115000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>114600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>116100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>120200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>138200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>135100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>142100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>151600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>182700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>183900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>188300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>187700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>182600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>164600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>153600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>119900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>114300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>111000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>129200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>138000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>138700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>130300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>135500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>142000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>147600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>138600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>131200</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3860,8 +3956,8 @@
       <c r="O44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3917,8 +4013,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3940,14 +4039,14 @@
       <c r="I45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J45" s="3">
-        <v>8900</v>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K45" s="3">
         <v>8900</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>8</v>
+      <c r="L45" s="3">
+        <v>8900</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>8</v>
@@ -3958,163 +4057,169 @@
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3">
         <v>6600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>16000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7800</v>
-      </c>
-      <c r="T45" s="3">
-        <v>6700</v>
       </c>
       <c r="U45" s="3">
         <v>6700</v>
       </c>
       <c r="V45" s="3">
+        <v>6700</v>
+      </c>
+      <c r="W45" s="3">
         <v>7200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>8100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>7100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>6000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>6200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>8000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>7700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>7400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>7100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>8100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>7000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>6800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>181100</v>
+      </c>
+      <c r="E46" s="3">
         <v>193200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>188200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>203700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>195200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>201700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>211500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>240800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>251300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>242200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>253500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>264100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>262600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>278700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>262200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>308500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>277800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>260000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>233300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>235300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>212000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>218600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>231500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>231000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>182000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>189400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>183400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>191700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>198000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>195400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>172500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>194900</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4154,8 +4259,8 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4211,204 +4316,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E48" s="3">
         <v>25700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>26600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>27000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>28000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>29500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>26900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>17500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>28600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>30000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>31200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>32600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>35200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>36500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>35200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>38100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>40500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>42700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>45200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>49000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>52300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>56200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>57900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>63000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>65100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>66100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>26600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>25700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>23700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>22600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>22400</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>44700</v>
+      </c>
+      <c r="E49" s="3">
         <v>45400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>46500</v>
       </c>
-      <c r="F49" s="3">
-        <v>68500</v>
-      </c>
       <c r="G49" s="3">
+        <v>47700</v>
+      </c>
+      <c r="H49" s="3">
         <v>118400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>182000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>243800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>242300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>242000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>241400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>226300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>224200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>222000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>222800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>223100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>225500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>232800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>234200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>235600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>237000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>237100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>237300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>234800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>234100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>235100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>236400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>242200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>205400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>206700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>207700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>209400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>210500</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E52" s="3">
         <v>15600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>16300</v>
       </c>
-      <c r="F52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G52" s="3">
+        <v>17000</v>
+      </c>
+      <c r="H52" s="3">
         <v>17700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1400</v>
-      </c>
-      <c r="L52" s="3">
-        <v>1600</v>
       </c>
       <c r="M52" s="3">
         <v>1600</v>
       </c>
       <c r="N52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="O52" s="3">
         <v>1800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>13800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>12300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>12200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>11000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>6700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>6100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>5900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>5400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>4700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>4600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>4500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>4000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>274100</v>
+      </c>
+      <c r="E54" s="3">
         <v>289300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>287200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>304700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>375600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>424900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>512900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>510900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>523200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>524900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>522400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>532000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>532300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>550500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>534000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>581500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>559700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>538200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>514600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>520600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>501600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>512000</v>
-      </c>
-      <c r="Y54" s="3">
-        <v>529200</v>
       </c>
       <c r="Z54" s="3">
         <v>529200</v>
       </c>
       <c r="AA54" s="3">
+        <v>529200</v>
+      </c>
+      <c r="AB54" s="3">
         <v>486000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>496400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>496600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>428400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>435100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>431300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>408400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>432700</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,148 +5099,152 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11500</v>
+      </c>
+      <c r="E57" s="3">
         <v>11700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>12400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>13600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>14000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>15200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>17400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>17500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>15700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>14500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>16500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>16600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>12900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>13600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>17800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>15900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>18100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>16000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>17500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>20300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>15300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>15800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>18600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>20100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>22800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>21600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>22400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>22300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>22000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>23300</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E58" s="3">
         <v>4900</v>
-      </c>
-      <c r="E58" s="3">
-        <v>5100</v>
       </c>
       <c r="F58" s="3">
         <v>5100</v>
       </c>
       <c r="G58" s="3">
+        <v>5100</v>
+      </c>
+      <c r="H58" s="3">
         <v>5300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>7500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7700</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -5165,290 +5299,299 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E59" s="3">
         <v>17700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>8400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>10700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13400</v>
-      </c>
-      <c r="M59" s="3">
-        <v>10400</v>
       </c>
       <c r="N59" s="3">
         <v>10400</v>
       </c>
       <c r="O59" s="3">
+        <v>10400</v>
+      </c>
+      <c r="P59" s="3">
         <v>11100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>84400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>78900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>110700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>97900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>83200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>77200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>84900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>85900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>71300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>72800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>79100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>72200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>77900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>66300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>69800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>58900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>63300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>50600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>71200</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>66100</v>
+      </c>
+      <c r="E60" s="3">
         <v>73100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>58600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>75400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>74200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>73600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>74600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>72400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>84100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>86800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>83900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>97100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>102100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>101000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>91800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>124300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>115600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>99100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>95400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>100900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>103400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>91600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>88100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>94900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>90800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>97900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>89000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>91400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>81300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>85600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>72600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>94500</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E61" s="3">
         <v>19800</v>
-      </c>
-      <c r="E61" s="3">
-        <v>20200</v>
       </c>
       <c r="F61" s="3">
         <v>20200</v>
       </c>
       <c r="G61" s="3">
+        <v>20200</v>
+      </c>
+      <c r="H61" s="3">
         <v>21300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>22400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>19300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>9800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11500</v>
-      </c>
-      <c r="P61" s="3">
-        <v>20000</v>
       </c>
       <c r="Q61" s="3">
         <v>20000</v>
       </c>
       <c r="R61" s="3">
-        <v>54000</v>
+        <v>20000</v>
       </c>
       <c r="S61" s="3">
         <v>54000</v>
       </c>
       <c r="T61" s="3">
+        <v>54000</v>
+      </c>
+      <c r="U61" s="3">
         <v>44000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>33000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>43000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>53000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>68000</v>
-      </c>
-      <c r="Y61" s="3">
-        <v>88000</v>
       </c>
       <c r="Z61" s="3">
         <v>88000</v>
       </c>
       <c r="AA61" s="3">
+        <v>88000</v>
+      </c>
+      <c r="AB61" s="3">
         <v>49000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>54000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>73000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>43000</v>
-      </c>
-      <c r="AE61" s="3">
-        <v>58000</v>
       </c>
       <c r="AF61" s="3">
         <v>58000</v>
@@ -5457,10 +5600,13 @@
         <v>58000</v>
       </c>
       <c r="AH61" s="3">
+        <v>58000</v>
+      </c>
+      <c r="AI61" s="3">
         <v>63000</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5468,97 +5614,100 @@
         <v>1800</v>
       </c>
       <c r="E62" s="3">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="F62" s="3">
         <v>2000</v>
       </c>
       <c r="G62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H62" s="3">
         <v>2200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2500</v>
-      </c>
-      <c r="K62" s="3">
-        <v>5300</v>
       </c>
       <c r="L62" s="3">
         <v>5300</v>
       </c>
       <c r="M62" s="3">
+        <v>5300</v>
+      </c>
+      <c r="N62" s="3">
         <v>3100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>27400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>30300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>30700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>33100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>41500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>45400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>47200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>37600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>45400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>43200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>42600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>43400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>44200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>46200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>11600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>12500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>10300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>9500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>6300</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>87400</v>
+      </c>
+      <c r="E66" s="3">
         <v>94700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>80900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>97600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>97800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>99200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>105700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>92200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>108300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>111300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>103500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>117500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>125500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>148400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>142100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>209000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>202700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>184600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>173800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>191100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>194000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>205000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>219200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>225500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>183200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>196100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>208200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>146000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>151800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>153900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>140100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>163800</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-155500</v>
+      </c>
+      <c r="E72" s="3">
         <v>-141700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-126900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-121600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-45900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>78000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>88600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>83000</v>
-      </c>
-      <c r="L72" s="3">
-        <v>85900</v>
       </c>
       <c r="M72" s="3">
         <v>85900</v>
       </c>
       <c r="N72" s="3">
+        <v>85900</v>
+      </c>
+      <c r="O72" s="3">
         <v>87600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>80700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>78600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>66100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>52700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>36900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>22200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>375400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>367200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>348700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>352700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>358300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>360500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>361000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>358500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>350700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>350200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>345000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>343800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>337400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>335700</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>186700</v>
+      </c>
+      <c r="E76" s="3">
         <v>194600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>206400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>207100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>277800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>325700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>407200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>418800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>414900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>413600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>418800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>414500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>406800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>402100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>392000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>372400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>357000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>353600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>340800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>329500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>307600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>306900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>309900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>303700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>302800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>300300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>288400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>282400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>283300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>277400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>268300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>268800</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46081</v>
+      </c>
+      <c r="E80" s="2">
         <v>45990</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45899</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45808</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45710</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45619</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45528</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45437</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45346</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45255</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45164</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45073</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44982</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44891</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44800</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44709</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44618</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44528</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44436</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44345</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44254</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44163</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44072</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43981</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43883</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43792</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43701</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43610</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43519</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43428</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43337</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43246</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-12700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-2400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-73300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-44100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-68700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-5700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>10500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>11800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>17400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>18100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>20500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>19400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>14300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>12900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>23200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>2300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>4100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>6900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>12300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>4900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>9400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>5800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>10600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>5700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>4000</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7211,19 +7410,19 @@
         <v>1900</v>
       </c>
       <c r="E83" s="3">
+        <v>1900</v>
+      </c>
+      <c r="F83" s="3">
         <v>2000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>800</v>
-      </c>
-      <c r="I83" s="3">
-        <v>900</v>
       </c>
       <c r="J83" s="3">
         <v>900</v>
@@ -7244,64 +7443,67 @@
         <v>900</v>
       </c>
       <c r="P83" s="3">
-        <v>2100</v>
+        <v>900</v>
       </c>
       <c r="Q83" s="3">
         <v>2100</v>
       </c>
       <c r="R83" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="S83" s="3">
         <v>2200</v>
       </c>
       <c r="T83" s="3">
+        <v>2200</v>
+      </c>
+      <c r="U83" s="3">
         <v>2100</v>
-      </c>
-      <c r="U83" s="3">
-        <v>2000</v>
       </c>
       <c r="V83" s="3">
         <v>2000</v>
       </c>
       <c r="W83" s="3">
+        <v>2000</v>
+      </c>
+      <c r="X83" s="3">
         <v>2200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>2400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2500</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>2700</v>
       </c>
       <c r="AA83" s="3">
         <v>2700</v>
       </c>
       <c r="AB83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="AC83" s="3">
         <v>2900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>2500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>2200</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>2100</v>
       </c>
       <c r="AF83" s="3">
         <v>2100</v>
       </c>
       <c r="AG83" s="3">
+        <v>2100</v>
+      </c>
+      <c r="AH83" s="3">
         <v>2000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>2100</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8700</v>
+      </c>
+      <c r="E89" s="3">
         <v>15900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>16800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>20500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-2200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>17800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>40200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>29000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-5300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>26800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>19200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>4600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>5800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>11000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>18600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>28000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>4300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>20300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>30100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>11800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>18300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-16600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>17600</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,64 +8144,65 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-300</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-100</v>
       </c>
       <c r="K91" s="3">
         <v>-100</v>
       </c>
       <c r="L91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-700</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-300</v>
       </c>
       <c r="S91" s="3">
         <v>-300</v>
       </c>
       <c r="T91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="U91" s="3">
         <v>-1300</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-1000</v>
       </c>
       <c r="V91" s="3">
         <v>-1000</v>
@@ -7990,40 +8211,43 @@
         <v>-1000</v>
       </c>
       <c r="X91" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-1500</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-300</v>
       </c>
       <c r="Z91" s="3">
         <v>-300</v>
       </c>
       <c r="AA91" s="3">
-        <v>-800</v>
+        <v>-300</v>
       </c>
       <c r="AB91" s="3">
         <v>-800</v>
       </c>
       <c r="AC91" s="3">
+        <v>-800</v>
+      </c>
+      <c r="AD91" s="3">
         <v>-500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>2400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>2300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1300</v>
-      </c>
-      <c r="U94" s="3">
-        <v>-1000</v>
       </c>
       <c r="V94" s="3">
         <v>-1000</v>
       </c>
       <c r="W94" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="X94" s="3">
         <v>-1200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-24800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-6900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-600</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,25 +8585,26 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="E96" s="3">
         <v>2300</v>
       </c>
       <c r="F96" s="3">
-        <v>4600</v>
+        <v>2300</v>
       </c>
       <c r="G96" s="3">
         <v>4600</v>
       </c>
       <c r="H96" s="3">
-        <v>4700</v>
+        <v>4600</v>
       </c>
       <c r="I96" s="3">
         <v>4700</v>
@@ -8394,19 +8628,19 @@
         <v>4700</v>
       </c>
       <c r="P96" s="3">
+        <v>4700</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-4700</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-4600</v>
       </c>
       <c r="R96" s="3">
         <v>-4600</v>
       </c>
       <c r="S96" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="T96" s="3">
         <v>-4700</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-4600</v>
       </c>
       <c r="U96" s="3">
         <v>-4600</v>
@@ -8418,7 +8652,7 @@
         <v>-4600</v>
       </c>
       <c r="X96" s="3">
-        <v>-4500</v>
+        <v>-4600</v>
       </c>
       <c r="Y96" s="3">
         <v>-4500</v>
@@ -8433,7 +8667,7 @@
         <v>-4500</v>
       </c>
       <c r="AC96" s="3">
-        <v>-4100</v>
+        <v>-4500</v>
       </c>
       <c r="AD96" s="3">
         <v>-4100</v>
@@ -8445,13 +8679,16 @@
         <v>-4100</v>
       </c>
       <c r="AG96" s="3">
-        <v>-3800</v>
+        <v>-4100</v>
       </c>
       <c r="AH96" s="3">
         <v>-3800</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>-3800</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-5700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-9700</v>
-      </c>
-      <c r="I100" s="3">
-        <v>-7700</v>
       </c>
       <c r="J100" s="3">
         <v>-7700</v>
       </c>
       <c r="K100" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="L100" s="3">
         <v>-1700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-9700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-7600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-25900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-9300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-29100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-7100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>8100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-11400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-13500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-16900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-27600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>32700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-10300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-22300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>30700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-28000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-11700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-4800</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1800</v>
-      </c>
-      <c r="E101" s="3">
-        <v>-300</v>
       </c>
       <c r="F101" s="3">
         <v>-300</v>
       </c>
       <c r="G101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="H101" s="3">
         <v>-400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-1000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>2100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-100</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>-200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-500</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E102" s="3">
         <v>12300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-8600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>13700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-11400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-19300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>18100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-16800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>12900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>14500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>16900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-31600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>22300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>11600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>8700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-12500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-9600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-13200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-17400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>18900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>59700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-7100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>2700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-4900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>7100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>13800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-29400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>13300</v>
       </c>
     </row>
